--- a/charsheet/template.xlsx
+++ b/charsheet/template.xlsx
@@ -9889,7 +9889,7 @@
       <c r="AH3" s="49"/>
       <c r="AI3" s="50"/>
       <c r="AJ3" s="63" t="str">
-        <f>ifs(
+        <f>_xlfn.IFS(
 AB13&gt;=AB5,"死亡",
 AB9+AB11+AB13-AB5&gt;0,"需要轉化傷勢",
 AB7+AB9+AB11+AB13&gt;0,"存活"
@@ -12378,7 +12378,7 @@
       <c r="A15" s="106"/>
       <c r="B15" s="107" t="str">
         <f>IFERROR(
-ifs(SUM($F$18:$G$26)=18,"請在建卡欄位分配您的屬性(3+2+1/6)，單屬性上限為5，總和為30。",
+_xlfn.IFS(SUM($F$18:$G$26)=18,"請在建卡欄位分配您的屬性(3+2+1/6)，單屬性上限為5，總和為30。",
 SUMIF($F$18:$G$26,"&gt;5")&gt;0,"創角點數上限為5，請檢查。",
 SUM($F$18:$G$26)+COUNTIF($F$18:$G$26,"&gt;4")=30,"創卡屬性分配完成。"),"請在建卡欄位分配您的屬性(3+2+1/6)，單屬性上限為5，總和為30。剩餘點數："&amp;(30-SUM($F$18:$F$26)-COUNTIF($F$18:$F$26,"&gt;4")))</f>
         <v>請在建卡欄位分配您的屬性(3+2+1/6)，單屬性上限為5，總和為30。</v>
@@ -15059,7 +15059,7 @@
       <c r="A27" s="106"/>
       <c r="B27" s="107" t="str">
         <f>IFERROR(
-ifs(SUM(G30:H55)=0,"請在建卡欄位分配您的技能(6+5+4/5)，單技能上限為5，總和為20。",
+_xlfn.IFS(SUM(G30:H55)=0,"請在建卡欄位分配您的技能(6+5+4/5)，單技能上限為5，總和為20。",
 SUMIF(G30:H55,"&gt;5")&gt;0,"創角技能上限為5，請檢查。",
 SUM(G30:H55)+countif(G30:G55,"&gt;3")+countif(G30:G55,"&gt;4")=20,"創卡技能分配完成。"),"請在建卡欄位分配您的技能(6+5+4/5)，單技能上限為5，總和為20。剩餘點數："&amp;(20-SUM(G30:H55)-countif(G30:G55,"&gt;3")-countif(G30:G55,"&gt;4")))</f>
         <v>請在建卡欄位分配您的技能(6+5+4/5)，單技能上限為5，總和為20。</v>
@@ -17099,7 +17099,7 @@
       <c r="BE36" s="46"/>
       <c r="BF36" s="47"/>
       <c r="BG36" s="200" t="str">
-        <f t="shared" ref="BG36:BG39" si="13">iferror(VLOOKUP(AU36,$CZ$155:$DI$186,5,false)+vlookup(AF36,$CZ$155:$DI$186,5,false),"X")</f>
+        <f>iferror(VLOOKUP(AU36,$CZ$155:$DI$186,5,false)+vlookup(AF36,$CZ$155:$DI$186,5,false),"X")</f>
         <v>X</v>
       </c>
       <c r="BH36" s="47"/>
@@ -17319,7 +17319,7 @@
       <c r="BE37" s="46"/>
       <c r="BF37" s="47"/>
       <c r="BG37" s="200" t="str">
-        <f t="shared" si="13"/>
+        <f>iferror(VLOOKUP(AU37,$CZ$155:$DI$186,5,false)+vlookup(AF37,$CZ$155:$DI$186,5,false),"X")</f>
         <v>X</v>
       </c>
       <c r="BH37" s="47"/>
@@ -17754,7 +17754,7 @@
       <c r="BE39" s="46"/>
       <c r="BF39" s="47"/>
       <c r="BG39" s="200" t="str">
-        <f t="shared" si="13"/>
+        <f>iferror(VLOOKUP(AU39,$CZ$155:$DI$186,5,false)+vlookup(AF39,$CZ$155:$DI$186,5,false),"X")</f>
         <v>X</v>
       </c>
       <c r="BH39" s="47"/>
@@ -44692,12 +44692,12 @@
       <c r="CG165" s="49"/>
       <c r="CH165" s="50"/>
       <c r="CI165" s="516">
-        <f>ifs(CE165="XP",ifs(CK157,ifs(
+        <f>_xlfn.IFS(CE165="XP",_xlfn.IFS(CK157,_xlfn.IFS(
 CL155=0,((((CK161-1)+CL155)*(CK161-CL155))*2+1),
 CL155&gt;0,(((CK161-1)+CL155)*(CK161-CL155))*2),
 CK159=0,((((CK161-1)+CK159)*(CK161-CK159))*2+1),
 CK159&gt;0,(((CK161-1)+CK159)*(CK161-CK159))*2),
-CE165="點數",ifs(CK157,ifs(
+CE165="點數",_xlfn.IFS(CK157,_xlfn.IFS(
 CL155=0,((((CK161-1)+CL155)*(CK161-CL155))*100+100),
 CL155&gt;0,(((CK161-1)+CL155)*(CK161-CL155))*100),
 CK159=0,((((CK161-1)+CK159)*(CK161-CK159))*100+100),
@@ -44717,7 +44717,7 @@
       <c r="CR165" s="49"/>
       <c r="CS165" s="50"/>
       <c r="CT165" s="516">
-        <f>ifs(CV157,ifs(
+        <f>_xlfn.IFS(CV157,_xlfn.IFS(
 CW155=0,((((CV161-1)+CW155)*(CV161-CW155))+1),
 CW155&gt;0,(((CV161-1)+CW155)*(CV161-CW155))),
 CV159=0,((((CV161-1)+CV159)*(CV161-CV159))+1),
@@ -46969,7 +46969,7 @@
       </c>
       <c r="CV176" s="522">
         <f>((CV172*(CV172+1))/2-(CV170*(CV170+1))/2)
-*IFS(CV174="普通",3,CV174="輪迴隊",6)</f>
+*_xlfn.IFS(CV174="普通",3,CV174="輪迴隊",6)</f>
         <v>9</v>
       </c>
       <c r="CY176" s="60"/>

--- a/charsheet/template.xlsx
+++ b/charsheet/template.xlsx
@@ -16460,7 +16460,7 @@
       <c r="BN33" s="46"/>
       <c r="BO33" s="47"/>
       <c r="BP33" s="209">
-        <f t="array" ref="BP33">V18+V19+LOOKUP(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},{8,16,0,5,12,1,2,5})</f>
+        <f t="array" ref="BP33">V18+V19+INDEX({8,16,0,5,12,1,2,5},MATCH(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},0))</f>
         <v>9</v>
       </c>
       <c r="BQ33" s="46"/>
@@ -17336,7 +17336,7 @@
       <c r="BN37" s="46"/>
       <c r="BO37" s="47"/>
       <c r="BP37" s="209">
-        <f t="array" ref="BP37">V20+LOOKUP(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},{17,37,0,10,26,1,2,5})</f>
+        <f t="array" ref="BP37">V20+INDEX({17,37,0,10,26,1,2,5},MATCH(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},0))</f>
         <v>7</v>
       </c>
       <c r="BQ37" s="46"/>
@@ -17556,7 +17556,7 @@
       <c r="BN38" s="46"/>
       <c r="BO38" s="47"/>
       <c r="BP38" s="209">
-        <f t="array" ref="BP38">LOOKUP(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},{4,8,0,2,6,0,2,2})</f>
+        <f t="array" ref="BP38">INDEX({4,8,0,2,6,0,2,2},MATCH(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},0))</f>
         <v>2</v>
       </c>
       <c r="BQ38" s="46"/>
@@ -40759,9 +40759,9 @@
       <c r="AT147" s="49"/>
       <c r="AU147" s="50"/>
       <c r="AV147" s="481" t="str">
-        <f t="array" ref="AV147">"輕度負荷:"&amp;ROUNDDOWN((13+(V18-1)*3)*(X18+1)*LOOKUP(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},{3,5,1/4,2,4,1/3,1/2,1}),0)&amp;"公斤以下"&amp;
-"　/　中度負荷:"&amp;ROUNDDOWN(((13+(V18-1)*3)+1)*2*(X18+1)*LOOKUP(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},{3,5,1/4,2,4,1/3,1/2,1}),0)&amp;"公斤以下"&amp;
-"　/　重度負荷:"&amp;ROUNDDOWN(((((13+(V18-1)*3)+1)*2+1)+(13+(V18-1)*3)+1)*(X18+1)*LOOKUP(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},{3,5,1/4,2,4,1/3,1/2,1}),0)&amp;"公斤以下"</f>
+        <f t="array" ref="AV147">"輕度負荷:"&amp;ROUNDDOWN((13+(V18-1)*3)*(X18+1)*INDEX({3,5,0.25,2,4,0.3333333333333333,0.5,1},MATCH(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},0)),0)&amp;"公斤以下"&amp;
+"　/　中度負荷:"&amp;ROUNDDOWN(((13+(V18-1)*3)+1)*2*(X18+1)*INDEX({3,5,0.25,2,4,0.3333333333333333,0.5,1},MATCH(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},0)),0)&amp;"公斤以下"&amp;
+"　/　重度負荷:"&amp;ROUNDDOWN(((((13+(V18-1)*3)+1)*2+1)+(13+(V18-1)*3)+1)*(X18+1)*INDEX({3,5,0.25,2,4,0.3333333333333333,0.5,1},MATCH(BM32,{"超大型","超巨型","超微型","大型","巨型","微型","小型","中型"},0)),0)&amp;"公斤以下"</f>
         <v>輕度負荷:16公斤以下　/　中度負荷:34公斤以下　/　重度負荷:52公斤以下</v>
       </c>
       <c r="AW147" s="49"/>

--- a/charsheet/template.xlsx
+++ b/charsheet/template.xlsx
@@ -9937,7 +9937,7 @@
       <c r="BL3" s="49"/>
       <c r="BM3" s="50"/>
       <c r="BN3" s="65">
-        <f>3+X24*2+if(BP54,BZ54,0)</f>
+        <f>3+X24*2+if((BP54&amp;""="TRUE"),BZ54,0)</f>
         <v>3</v>
       </c>
       <c r="BO3" s="49"/>
@@ -23511,7 +23511,7 @@
       <c r="CM64" s="352"/>
       <c r="CN64" s="318"/>
       <c r="CO64" s="418">
-        <f>IF(CU58=TRUE,0,BM36+if(CY58=TRUE,BM36,0))</f>
+        <f>IF((CU58&amp;""="TRUE"),0,BM36+if((CY58&amp;""="TRUE"),BM36,0))</f>
         <v>2</v>
       </c>
       <c r="CP64" s="46"/>
@@ -23519,7 +23519,7 @@
       <c r="CR64" s="46"/>
       <c r="CS64" s="47"/>
       <c r="CT64" s="419" t="str">
-        <f>IF(CU58=TRUE,0,CW64)</f>
+        <f>IF((CU58&amp;""="TRUE"),0,CW64)</f>
         <v/>
       </c>
       <c r="CU64" s="46"/>
@@ -23527,7 +23527,7 @@
       <c r="CW64" s="420"/>
       <c r="CX64" s="47"/>
       <c r="CY64" s="419">
-        <f>IF(CU58=TRUE,0,IF(DC58=TRUE,DB64,0))</f>
+        <f>IF((CU58&amp;""="TRUE"),0,IF((DC58&amp;""="TRUE"),DB64,0))</f>
         <v>0</v>
       </c>
       <c r="CZ64" s="46"/>
@@ -23970,7 +23970,7 @@
       <c r="CY66" s="46"/>
       <c r="CZ66" s="47"/>
       <c r="DA66" s="418">
-        <f>IF(DC58=TRUE,DD66,0)</f>
+        <f>IF((DC58&amp;""="TRUE"),DD66,0)</f>
         <v>0</v>
       </c>
       <c r="DB66" s="46"/>
@@ -23978,7 +23978,7 @@
       <c r="DD66" s="420"/>
       <c r="DE66" s="47"/>
       <c r="DF66" s="418">
-        <f>IF(DC58=TRUE,DI66,0)</f>
+        <f>IF((DC58&amp;""="TRUE"),DI66,0)</f>
         <v>0</v>
       </c>
       <c r="DG66" s="46"/>
@@ -24910,7 +24910,7 @@
       <c r="CM70" s="352"/>
       <c r="CN70" s="318"/>
       <c r="CO70" s="419">
-        <f>IF(DG58=TRUE,4,0)+CR70</f>
+        <f>IF((DG58&amp;""="TRUE"),4,0)+CR70</f>
         <v>0</v>
       </c>
       <c r="CP70" s="46"/>
@@ -44692,12 +44692,12 @@
       <c r="CG165" s="49"/>
       <c r="CH165" s="50"/>
       <c r="CI165" s="516">
-        <f>_xlfn.IFS(CE165="XP",_xlfn.IFS(CK157,_xlfn.IFS(
+        <f>_xlfn.IFS(CE165="XP",_xlfn.IFS((CK157&amp;""="TRUE"),_xlfn.IFS(
 CL155=0,((((CK161-1)+CL155)*(CK161-CL155))*2+1),
 CL155&gt;0,(((CK161-1)+CL155)*(CK161-CL155))*2),
 CK159=0,((((CK161-1)+CK159)*(CK161-CK159))*2+1),
 CK159&gt;0,(((CK161-1)+CK159)*(CK161-CK159))*2),
-CE165="點數",_xlfn.IFS(CK157,_xlfn.IFS(
+CE165="點數",_xlfn.IFS((CK157&amp;""="TRUE"),_xlfn.IFS(
 CL155=0,((((CK161-1)+CL155)*(CK161-CL155))*100+100),
 CL155&gt;0,(((CK161-1)+CL155)*(CK161-CL155))*100),
 CK159=0,((((CK161-1)+CK159)*(CK161-CK159))*100+100),
@@ -44717,7 +44717,7 @@
       <c r="CR165" s="49"/>
       <c r="CS165" s="50"/>
       <c r="CT165" s="516">
-        <f>_xlfn.IFS(CV157,_xlfn.IFS(
+        <f>_xlfn.IFS((CV157&amp;""="TRUE"),_xlfn.IFS(
 CW155=0,((((CV161-1)+CW155)*(CV161-CW155))+1),
 CW155&gt;0,(((CV161-1)+CW155)*(CV161-CW155))),
 CV159=0,((((CV161-1)+CV159)*(CV161-CV159))+1),
@@ -53118,6 +53118,9 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BP54 CU58 CY58 DC58 DG58 EH62 EK62 CK157 CV157">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="CE165">
       <formula1>"點數,XP"</formula1>
     </dataValidation>

--- a/charsheet/template.xlsx
+++ b/charsheet/template.xlsx
@@ -24,7 +24,7 @@
     <comment authorId="0" ref="C34">
       <text>
         <t xml:space="preserve">一點：可以打開構造簡單的鎖或者扒一個醉鬼的錢包。
-兩點：偷車不是問題，從粗心的人口袋裏掏東西也不是問題。
+兩點：偷車不是問題，從粗心的人口袋裡掏東西也不是問題。
 三點：可以解除警鈴或是增強它的性能。一般人稍不注意就被你暗算了。
 四點：你可以侵入各種地方，一邊和人握手一邊取走對方的金錶。
 五點：你可以卸載在五角大廈的炸彈，當然有可能是你安裝的。
@@ -34,104 +34,104 @@
     </comment>
     <comment authorId="0" ref="C26">
       <text>
-        <t xml:space="preserve">镇定自若的能力，头脑的反应速度，在压力下或紧急情况下保持冷静的能力。在超自然意义上，代表了人物心智的活力。
-任何有意愿应对外界刺激的存在都拥有沉着值。
-沉着为0的人物失去行为能力和自制力，无法对任何情况作出反应。他将会处于“昏迷”状态。</t>
+        <t xml:space="preserve">鎮定自若的能力，頭腦的反應速度，在壓力下或緊急情況下保持冷靜的能力。在超自然意義上，代表了人物心智的活力。
+任何有意願應對外界刺激的存在都擁有沉著值。
+沉著為0的人物失去行為能力和自制力，無法對任何情況作出反應。他將會處於“昏迷”狀態。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI49">
       <text>
-        <t xml:space="preserve">二阶本能觉醒： 
-本能觉醒的第二阶段意味着生物能从细胞层级控制自己的身体，最大程度的减少行动时被白白耗费的体力。</t>
+        <t xml:space="preserve">二階本能覺醒： 
+本能覺醒的第二階段意味著生物能從細胞層級控制自己的身體，最大程度的減少行動時被白白耗費的體力。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CO15">
       <text>
-        <t xml:space="preserve">怪癖是程度较轻的人物特征，不是天赋也不一定属于缺陷——只是你独特而与众不同的地方。例如，你十分“贪婪”，但如果你坚持只接受金币作为报酬，这就是你的一个怪癖。 
-每个怪癖可以提供给你2XP，你可选择至多5个怪癖，由此得到额外的10XP，你可以使用本XP在建卡的时候如常购买专长或者提升技能等级，但是必须在建卡的技能分配和专长点数分配结束后购买。
-当然你也可以在未来花费4XP去掉一个怪癖。
-怪癖区分为生理类和精神类。这个划分主要是提示玩家该怪癖的代表的优缺点。
-如果没有特殊说明，怪癖带来的加减值是专长加减值。</t>
+        <t xml:space="preserve">怪癖是程度較輕的人物特徵，不是天賦也不一定屬於缺陷——只是你獨特而與眾不同的地方。例如，你十分“貪婪”，但如果你堅持只接受金幣作為報酬，這就是你的一個怪癖。 
+每個怪癖可以提供給你2XP，你可選擇至多5個怪癖，由此得到額外的10XP，你可以使用本XP在建卡的時候如常購買專長或者提升技能等級，但是必須在建卡的技能分配和專長點數分配結束後購買。
+當然你也可以在未來花費4XP去掉一個怪癖。
+怪癖區分為生理類和精神類。這個劃分主要是提示玩家該怪癖的代表的優缺點。
+如果沒有特殊說明，怪癖帶來的加減值是專長加減值。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BK49">
       <text>
-        <t xml:space="preserve">被动开启：
-当你一阶本能觉醒开启之后，且度过了一个冒险世界之后（包括开启一阶的那场），你在面临相似的情况时，可以获得一次提升本能觉醒层级的机会。你投掷一个2D10，若结果在18或18以上，则你成功的开启了第二阶的本能觉醒。
-（如你在第一个冒险世界一阶本能觉醒，则你只能在第二个世界之后才能进行二阶本能觉醒）</t>
+        <t xml:space="preserve">被動開啟：
+當你一階本能覺醒開啟之後，且度過了一個冒險世界之後（包括開啟一階的那場），你在面臨相似的情況時，可以獲得一次提升本能覺醒層級的機會。你投擲一個2D10，若結果在18或18以上，則你成功的開啟了第二階的本能覺醒。
+（如你在第一個冒險世界一階本能覺醒，則你只能在第二個世界之後才能進行二階本能覺醒）</t>
       </text>
     </comment>
     <comment authorId="0" ref="B84">
       <text>
-        <t xml:space="preserve">能力等级：
-能力拥有6个支线等级：无支线，D,C,B,A,S。双支线等于单支线等级。S级以上的能力皆视为S级，没有双S或者更多S的级别能力。
-如无特别说明，则视为其购买价格的等级。 
-能力等级在其购买时就已经决定了，除非特殊说明，否则【不会自动升级】或者【降级】。</t>
+        <t xml:space="preserve">能力等級：
+能力擁有6個支線等級：無支線，D,C,B,A,S。雙支線等於單支線等級。S級以上的能力皆視為S級，沒有雙S或者更多S的級別能力。
+如無特別說明，則視為其購買價格的等級。 
+能力等級在其購買時就已經決定了，除非特殊說明，否則【不會自動升級】或者【降級】。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C18">
       <text>
-        <t xml:space="preserve">推拉物体、举起重物等的相关属性，包括了爆发力和负重能力，因此也影响奔走或挥动物体的速度、击打时所能造成的伤害程度。
-任何能够对物体施加物理作用的存在都拥有力量值。
-力量为0的人物不能移动，无法承受自身的重量也无法移动肢体。他将会倒在地上，处于“倒地”状态，并且失去所有动作。</t>
+        <t xml:space="preserve">推拉物體、舉起重物等的相關屬性，包括了爆發力和負重能力，因此也影響奔走或揮動物體的速度、擊打時所能造成的傷害程度。
+任何能夠對物體施加物理作用的存在都擁有力量值。
+力量為0的人物不能移動，無法承受自身的重量也無法移動肢體。他將會倒在地上，處於“倒地”狀態，並且失去所有動作。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BN49">
       <text>
-        <t xml:space="preserve">主动开启：当你已经成功通过上述方法开启过一次二阶本能觉醒后，若你处于一阶本能觉醒的状态，你便可以通过一个标准动作，并且支付1点意志力来开启二阶本能觉醒。</t>
+        <t xml:space="preserve">主動開啟：當你已經成功通過上述方法開啟過一次二階本能覺醒後，若你處於一階本能覺醒的狀態，你便可以通過一個標準動作，並且支付1點意志力來開啟二階本能覺醒。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BQ49">
       <text>
-        <t xml:space="preserve">解除：解除二阶本能觉醒是一个自由动作。注意你会直接解除所有本能觉醒层阶，而不是从二阶退回一阶。</t>
+        <t xml:space="preserve">解除：解除二階本能覺醒是一個自由動作。注意你會直接解除所有本能覺醒層階，而不是從二階退回一階。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B142">
       <text>
-        <t xml:space="preserve">饰品（护符）：每个角色只有一个护符可以生效。</t>
+        <t xml:space="preserve">飾品（護符）：每個角色只有一個護符可以生效。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B109">
       <text>
-        <t xml:space="preserve">技艺/招式/法术等
-大多数依靠技巧的能力都被归于此项，尽管有时多种技艺可能提高同一能力（如某种心法能使你持续提高防御，而某种护身劲是在受到攻击时将能量集中来提供防御，它们同样提供防御，但可能不会叠加），技艺最大的特点是，它需要人物主动使用，而非被动生效。
-技艺包含招式、心法、身法、护身劲、技能、法术等等，这些可以分别启动。
-技艺一般为超自然能力，除非技艺本身具备特殊说明。 </t>
+        <t xml:space="preserve">技藝/招式/法術等
+大多數依靠技巧的能力都被歸於此項，儘管有時多種技藝可能提高同一能力（如某種心法能使你持續提高防禦，而某種護身勁是在受到攻擊時將能量集中來提供防禦，它們同樣提供防禦，但可能不會疊加），技藝最大的特點是，它需要人物主動使用，而非被動生效。
+技藝包含招式、心法、身法、護身勁、技能、法術等等，這些可以分別啟動。
+技藝一般為超自然能力，除非技藝本身具備特殊說明。 </t>
       </text>
     </comment>
     <comment authorId="0" ref="BS49">
       <text>
-        <t xml:space="preserve">效果：当你处于解开二阶本能觉醒状态时，你保留一阶本能觉醒的全部效果。并且你在使用意志力的基础用法时，一阶本能觉醒的效果改为获得等于感知和智力中较高者的加值，而非较低者。
-此外，你选择一项生理属性，在这个属性上你获得6点完美加值，并且该属性的相关检定获得2个额外的附加成功，你可以以一个迅捷动作变更所选的属性。
-额外奖励：只有第一次，当成功开启二阶本能觉醒时，ST应当给予玩家一次超常表现奖励。</t>
+        <t xml:space="preserve">效果：當你處於解開二階本能覺醒狀態時，你保留一階本能覺醒的全部效果。並且你在使用意志力的基礎用法時，一階本能覺醒的效果改為獲得等於感知和智力中較高者的加值，而非較低者。
+此外，你選擇一項生理屬性，在這個屬性上你獲得6點完美加值，並且該屬性的相關檢定獲得2個額外的附加成功，你可以以一個迅捷動作變更所選的屬性。
+額外獎勵：只有第一次，當成功開啟二階本能覺醒時，ST應當給予玩家一次超常表現獎勵。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BX49">
       <text>
-        <t xml:space="preserve">持续时间：需要注意的是，开启二阶本能觉醒必须在开启一阶本能觉醒的前提下，同时解除二阶本能觉醒会自动解除一阶本能觉醒，所以二阶没有额外的能耗（一阶每轮消耗1点意志力代为支付）。</t>
+        <t xml:space="preserve">持續時間：需要注意的是，開啟二階本能覺醒必須在開啟一階本能覺醒的前提下，同時解除二階本能覺醒會自動解除一階本能覺醒，所以二階沒有額外的能耗（一階每輪消耗1點意志力代為支付）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI33">
       <text>
-        <t xml:space="preserve">战斗速度：战斗速度表示角色用一次移动动作能移动多远的距离，初始值为力量+敏捷+体积带来的基础速度修正，单位是米，该速度也被称之为基础移动速度。
+        <t xml:space="preserve">戰鬥速度：戰鬥速度表示角色用一次移動動作能移動多遠的距離，初始值為力量+敏捷+體積帶來的基礎速度修正，單位是米，該速度也被稱之為基礎移動速度。
 </t>
       </text>
     </comment>
     <comment authorId="0" ref="CO65">
       <text>
-        <t xml:space="preserve">天生防御：
-天生防御只会加在防御上，它意味着你的皮肤厚重、肌肉坚硬或骨骼坚不可摧。
-天生防御不会叠加。</t>
+        <t xml:space="preserve">天生防禦：
+天生防禦只會加在防禦上，它意味著你的皮膚厚重、肌肉堅硬或骨骼堅不可摧。
+天生防禦不會疊加。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B134">
       <text>
-        <t xml:space="preserve">披风：披在肩膀上的装备，一般为魔幻本质特有，每个角色只有一个披风位。</t>
+        <t xml:space="preserve">披風：披在肩膀上的裝備，一般為魔幻本質特有，每個角色只有一個披風位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="X26">
       <text>
-        <t xml:space="preserve">在沉着相关的检定上获得n个附加成功。
+        <t xml:space="preserve">在沉著相關的檢定上獲得n個附加成功。
 意志力池提升3n。
 先攻提升3n。</t>
       </text>
@@ -149,64 +149,64 @@
     </comment>
     <comment authorId="0" ref="CT65">
       <text>
-        <t xml:space="preserve">盔甲防御：
-盔甲防御只会加在防御上，它意味着你穿着防护性的护具。
-盔甲防御不会叠加。</t>
+        <t xml:space="preserve">盔甲防禦：
+盔甲防禦只會加在防禦上，它意味著你穿著防護性的護具。
+盔甲防禦不會疊加。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Q142">
       <text>
-        <t xml:space="preserve">概念武装：这是一种特殊的装备，其可能是一件装备也可能是一个概念，当其是装备时，同时占用概念武装位以及对应的装备位，每个角色只有一个概念武装位。
-若其附加在一个装备上时，当失去该装备时，一同失去该概念武装（包括击落，破坏等），若其自身即是一个装备时，其也会如常被破坏。</t>
+        <t xml:space="preserve">概念武裝：這是一種特殊的裝備，其可能是一件裝備也可能是一個概念，當其是裝備時，同時佔用概念武裝位以及對應的裝備位，每個角色只有一個概念武裝位。
+若其附加在一個裝備上時，當失去該裝備時，一同失去該概念武裝（包括擊落，破壞等），若其自身即是一個裝備時，其也會如常被破壞。</t>
       </text>
     </comment>
     <comment authorId="0" ref="X18">
       <text>
-        <t xml:space="preserve">在力量相关的检定上获得n个附加成功。
-人物的负重能力*n+1倍。
-极限投掷距离以及弓箭极限射程*n+1倍。
-进行力量相关的检定时获得nDP的完美加值。
-以力量进行攻击时，你的伤害上限提升n(n+1)/2。</t>
+        <t xml:space="preserve">在力量相關的檢定上獲得n個附加成功。
+人物的負重能力*n+1倍。
+極限投擲距離以及弓箭極限射程*n+1倍。
+進行力量相關的檢定時獲得nDP的完美加值。
+以力量進行攻擊時，你的傷害上限提升n(n+1)/2。</t>
       </text>
     </comment>
     <comment authorId="0" ref="DA65">
       <text>
-        <t xml:space="preserve">盾牌防御：
-盾牌防御只会加在防御上，它意味着你使用盾牌或者类似武器进行格挡。
-盾牌防御不会叠加。</t>
+        <t xml:space="preserve">盾牌防禦：
+盾牌防禦只會加在防禦上，它意味著你使用盾牌或者類似武器進行格擋。
+盾牌防禦不會疊加。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI50">
       <text>
-        <t xml:space="preserve">三阶本能觉醒：
-本能觉醒的第三阶段开始从外转内，它允许你不断的开发自己的脑域，或者是模拟他人的思维模式。</t>
+        <t xml:space="preserve">三階本能覺醒：
+本能覺醒的第三階段開始從外轉內，它允許你不斷的開發自己的腦域，或者是模擬他人的思維模式。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Q134">
       <text>
-        <t xml:space="preserve">盔甲：盔甲一般包括上衣和裤子，除非有特殊说明，无论如何，装备一个盔甲之后无法装备另外一个盔甲。</t>
+        <t xml:space="preserve">盔甲：盔甲一般包括上衣和褲子，除非有特殊說明，無論如何，裝備一個盔甲之後無法裝備另外一個盔甲。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C19">
       <text>
-        <t xml:space="preserve">全身的协调能力、动作的精确性和灵活性、反应神经等，快速有效运动身体的能力。
-任何能够活动和移动的物体都拥有敏捷值。
-敏捷为0的人物不能活动，关节僵死。他将会倒在地上，处于“倒地”状态，并且失去所有动作。</t>
+        <t xml:space="preserve">全身的協調能力、動作的精確性和靈活性、反應神經等，快速有效運動身體的能力。
+任何能夠活動和移動的物體都擁有敏捷值。
+敏捷為0的人物不能活動，關節僵死。他將會倒在地上，處於“倒地”狀態，並且失去所有動作。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BQ50">
       <text>
-        <t xml:space="preserve">主动开启：当你二阶本能觉醒开启之后，且度过了四个冒险世界（包括开启二阶的那场）之后，你可以自动开启三阶本能觉醒。
-若你处于二阶本能觉醒的状态，你可以通过一个自由动作，并且支付1点意志力来开启三阶本能觉醒。</t>
+        <t xml:space="preserve">主動開啟：當你二階本能覺醒開啟之後，且度過了四個冒險世界（包括開啟二階的那場）之後，你可以自動開啟三階本能覺醒。
+若你處於二階本能覺醒的狀態，你可以通過一個自由動作，並且支付1點意志力來開啟三階本能覺醒。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BT50">
       <text>
-        <t xml:space="preserve">效果：当你处于解开三阶本能觉醒状态时，你保留一、二阶本能觉醒带来的效果。此外，你可以模拟一个你熟悉的生命体的心智和社交属性，以及任何技能等级。但是你必须为你和目标之间的每点属性、每级技能差值支付2XP，你只能将属性模拟到对方的数值-5的程度，技能模拟到对方的数值-4的程度。只要你曾经支付过一次经验，你就无需为此数值之内的差值再度支付经验，但这个经验在你的属性、技能和专长提升之后是不会返还的。你不能将你的属性和技能模拟到你原本的两倍以上。
-这个熟悉的生命体一般视为与你经历过3场冒险世界以上的人员。
-当你累计为三阶本能觉醒投入了42XP之后，你获得开启四阶本能觉醒的权利。
-特殊说明：
-你模拟的目标属性和你自身的起步属性只计算起基本属性，内在属性和修行属性等，简单而言，这些属性都必须是持续时间为永久并且不可因为某些情况改变的，属性伤害和吸取不在此范畴内。
+        <t xml:space="preserve">效果：當你處於解開三階本能覺醒狀態時，你保留一、二階本能覺醒帶來的效果。此外，你可以模擬一個你熟悉的生命體的心智和社交屬性，以及任何技能等級。但是你必須為你和目標之間的每點屬性、每級技能差值支付2XP，你只能將屬性模擬到對方的數值-5的程度，技能模擬到對方的數值-4的程度。只要你曾經支付過一次經驗，你就無需為此數值之內的差值再度支付經驗，但這個經驗在你的屬性、技能和專長提升之後是不會返還的。你不能將你的屬性和技能模擬到你原本的兩倍以上。
+這個熟悉的生命體一般視為與你經歷過3場冒險世界以上的人員。
+當你累計為三階本能覺醒投入了42XP之後，你獲得開啟四階本能覺醒的權利。
+特殊說明：
+你模擬的目標屬性和你自身的起步屬性只計算起基本屬性，內在屬性和修行屬性等，簡單而言，這些屬性都必須是持續時間為永久並且不可因為某些情況改變的，屬性傷害和吸取不在此範疇內。
 </t>
       </text>
     </comment>
@@ -223,20 +223,20 @@
     </comment>
     <comment authorId="0" ref="BX50">
       <text>
-        <t xml:space="preserve">持续时间：需要注意的是，开启三阶本能觉醒必须在开启二阶本能觉醒的前提下，同时解除三阶本能觉醒会自动解除所有本能觉醒，所以三阶没有额外的能耗（一阶每轮消耗1点意志力代为支付）。</t>
+        <t xml:space="preserve">持續時間：需要注意的是，開啟三階本能覺醒必須在開啟二階本能覺醒的前提下，同時解除三階本能覺醒會自動解除所有本能覺醒，所以三階沒有額外的能耗（一階每輪消耗1點意志力代為支付）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AT84">
       <text>
-        <t xml:space="preserve">能力等级：
-能力拥有6个支线等级：无支线，D,C,B,A,S。双支线等于单支线等级。S级以上的能力皆视为S级，没有双S或者更多S的级别能力。
-如无特别说明，则视为其购买价格的等级。 
-能力等级在其购买时就已经决定了，除非特殊说明，否则【不会自动升级】或者【降级】。</t>
+        <t xml:space="preserve">能力等級：
+能力擁有6個支線等級：無支線，D,C,B,A,S。雙支線等於單支線等級。S級以上的能力皆視為S級，沒有雙S或者更多S的級別能力。
+如無特別說明，則視為其購買價格的等級。 
+能力等級在其購買時就已經決定了，除非特殊說明，否則【不會自動升級】或者【降級】。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI34">
       <text>
-        <t xml:space="preserve">旅行速度：旅行速度是一种特殊能力，角色在未来可能会掌握更快的从某个地点到另外一个地点的能力。在角色未拥有特殊能力下，该速度的初始值与基础移动速度相等。</t>
+        <t xml:space="preserve">旅行速度：旅行速度是一種特殊能力，角色在未來可能會掌握更快的從某個地點到另外一個地點的能力。在角色未擁有特殊能力下，該速度的初始值與基礎移動速度相等。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C36">
@@ -252,65 +252,65 @@
     </comment>
     <comment authorId="0" ref="CO58">
       <text>
-        <t xml:space="preserve">攻击行为的作用目标为【一个目标】的时候，需要【扣除目标防御】（无论是物理还是施法，又或者是心灵还是其他任何能力）。如果没有指定目标，而是范围所有的所有单位，则【不扣防御】。
-特殊：如进行力量+白刃检定，敏捷+运动检定此类检定不会扣除防御进行计算。
-对范围内所有目标分别进行攻击不属于范围伤害。
-对范围内的目标分别进行攻击，要分别对每个目标进行攻击检定。
-当你使用类似的能力时，你依然只能对你已经进行定位的目标进行攻击。
-该攻击本质上还是单体攻击。
-当一个行为（如近战白刃攻击，远程枪械攻击，施展法术）直接指定一个受影响的个体时，该个体被称为该能力的目标。从某种意义上，这个目标是施展该行为的一部分，因此如果施展者不能定位目标，该行为就不能施展，如单体指向性法术，群体指向性法术，单体攻击等。
-也有一些行为不影响个体，而是影响一个区域范围（如火球术，投掷手雷等），这种情况下，角色只需要指定范围，即使没有明确的对象，该行为也可以使用。若没有特殊说明，范围内的所有目标【皆受到影响，包括自己】</t>
+        <t xml:space="preserve">攻擊行為的作用目標為【一個目標】的時候，需要【扣除目標防禦】（無論是物理還是施法，又或者是心靈還是其他任何能力）。如果沒有指定目標，而是範圍所有的所有單位，則【不扣防禦】。
+特殊：如進行力量+白刃檢定，敏捷+運動檢定此類檢定不會扣除防禦進行計算。
+對範圍內所有目標分別進行攻擊不屬於範圍傷害。
+對範圍內的目標分別進行攻擊，要分別對每個目標進行攻擊檢定。
+當你使用類似的能力時，你依然只能對你已經進行定位的目標進行攻擊。
+該攻擊本質上還是單體攻擊。
+當一個行為（如近戰白刃攻擊，遠程槍械攻擊，施展法術）直接指定一個受影響的個體時，該個體被稱為該能力的目標。從某種意義上，這個目標是施展該行為的一部分，因此如果施展者不能定位目標，該行為就不能施展，如單體指向性法術，群體指向性法術，單體攻擊等。
+也有一些行為不影響個體，而是影響一個區域範圍（如火球術，投擲手雷等），這種情況下，角色只需要指定範圍，即使沒有明確的對象，該行為也可以使用。若沒有特殊說明，範圍內的所有目標【皆受到影響，包括自己】</t>
       </text>
     </comment>
     <comment authorId="0" ref="X19">
       <text>
-        <t xml:space="preserve">在敏捷相关的检定上获得n个附加成功。
-获得n点防御附加成功。
-基础防御增加n。
-反射豁免检定获得n*3DP完美加值。</t>
+        <t xml:space="preserve">在敏捷相關的檢定上獲得n個附加成功。
+獲得n點防禦附加成功。
+基礎防禦增加n。
+反射豁免檢定獲得n*3DP完美加值。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B28">
       <text>
-        <t xml:space="preserve">人物的技能定义了人物后天学习所得的，做某件具体事情的能力和技巧。
-与属性一样，它分为三大类技能，也就是生理系技能，心智系技能，互动系技能。
-生理系技能：运动、肉搏、驾驶、枪械、手上功夫、隐藏、求生、白刃
-心智系技能：学识、电脑、手艺（子分类）、调查、医学、神秘学、科学
-互动系技能：动物沟通、感受、表达（子分类）、胁迫、交际、掩饰
-除了技能之外，每项技能下还细分无数个“专业”，表现以特定方式使用技能。
-“专业”通常也由ST和PC协商决定，在“技能概述”章节中，我们列出了一些常用专业。
-当玩家在技能下拥有对应专业时，在使用该技能时，若符合该专业的用法时会获得1DP的专业加值。若没有特殊说明，专业加值无法让你在不进行检定的用法上获益。
+        <t xml:space="preserve">人物的技能定義了人物後天學習所得的，做某件具體事情的能力和技巧。
+與屬性一樣，它分為三大類技能，也就是生理系技能，心智系技能，互動系技能。
+生理系技能：運動、肉搏、駕駛、槍械、手上功夫、隱藏、求生、白刃
+心智系技能：學識、電腦、手藝（子分類）、調查、醫學、神秘學、科學
+互動系技能：動物溝通、感受、表達（子分類）、脅迫、交際、掩飾
+除了技能之外，每項技能下還細分無數個“專業”，表現以特定方式使用技能。
+“專業”通常也由ST和PC協商決定，在“技能概述”章節中，我們列出了一些常用專業。
+當玩家在技能下擁有對應專業時，在使用該技能時，若符合該專業的用法時會獲得1DP的專業加值。若沒有特殊說明，專業加值無法讓你在不進行檢定的用法上獲益。
 特殊的是：
-手艺技能以及表达技能并不是一项技能，而是一类技能的统称。手艺和表达可以有无数的技能子项，“手艺——烹饪”和“手艺——珠宝加工”显然是两项完全不同的技能，“表达——唱歌”以及“表达——舞蹈”明显也不是一个，这些拥有子技能的技能在学习的时候需要根据每个子技能分别学习，且使用该技能子项的时候，默认获得1DP专业加值。
-首先，将人物的所有技能基本值设置为0。
-将6点/5点/4点的点数按照这自身意愿任意分别分配给生理、心智、互动三类技能（你可以将6点分配给生理系技能，也可以将这6点分配给心智系），然后将点数加在各项技能上。
-然后，将5点自由点数任意加在想要提高的技能上。
-另外，将一项已经加到3的技能提升到4，需要耗费2点点数，若没有特殊说明，则无法在建卡的时候将技能突破4点。
-若拥有“特殊身份1级”则技能将突破4点，将一项已经加到4的技能提升到5，也需要耗费2点点数。
-另外，如同“技能概述”所述，每个到达3级和4级的技能，都可以分别免费获得一个对应该技能的专业，同时，你还额外获得3个专业，但是这3个专业必须放在你至少拥有1级等级的技能上。</t>
+手藝技能以及表達技能並不是一項技能，而是一類技能的統稱。手藝和表達可以有無數的技能子項，“手藝——烹飪”和“手藝——珠寶加工”顯然是兩項完全不同的技能，“表達——唱歌”以及“表達——舞蹈”明顯也不是一個，這些擁有子技能的技能在學習的時候需要根據每個子技能分別學習，且使用該技能子項的時候，默認獲得1DP專業加值。
+首先，將人物的所有技能基本值設置為0。
+將6點/5點/4點的點數按照這自身意願任意分別分配給生理、心智、互動三類技能（你可以將6點分配給生理系技能，也可以將這6點分配給心智系），然後將點數加在各項技能上。
+然後，將5點自由點數任意加在想要提高的技能上。
+另外，將一項已經加到3的技能提升到4，需要耗費2點點數，若沒有特殊說明，則無法在建卡的時候將技能突破4點。
+若擁有“特殊身份1級”則技能將突破4點，將一項已經加到4的技能提升到5，也需要耗費2點點數。
+另外，如同“技能概述”所述，每個到達3級和4級的技能，都可以分別免費獲得一個對應該技能的專業，同時，你還額外獲得3個專業，但是這3個專業必須放在你至少擁有1級等級的技能上。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CS58">
       <text>
         <t xml:space="preserve">措手不及
-措手不及是指人物没有办法及时做出反应。
-只有突袭轮以及特殊能力才会造成措手不及不良状态。
-在措手不及的状态下，人物将失去基础防御，闪避加值和格挡防御（不会失去盾牌防御），并且不能使用反射动作。
-措手不及是一个相对状态，在人物A，B，C三者间，可能B对A处于措手不及，但对C并无此状态。
-一般而言，每个造成措手不及状态的能力都有说明其措手不及的持续时间，若没有说明，则若该措手不及是由于自身原因造成的，如被突袭等，持续1轮或者到自己回合开始时结束。
-若该措手不及能力是由其他目标造成的，则若为攻击附带能力，则持续一次攻击，若为其他特殊能力，则持续到该目标回合结束后结束。</t>
+措手不及是指人物沒有辦法及時做出反應。
+只有突襲輪以及特殊能力才會造成措手不及不良狀態。
+在措手不及的狀態下，人物將失去基礎防禦，閃避加值和格擋防禦（不會失去盾牌防禦），並且不能使用反射動作。
+措手不及是一個相對狀態，在人物A，B，C三者間，可能B對A處於措手不及，但對C並無此狀態。
+一般而言，每個造成措手不及狀態的能力都有說明其措手不及的持續時間，若沒有說明，則若該措手不及是由於自身原因造成的，如被突襲等，持續1輪或者到自己回合開始時結束。
+若該措手不及能力是由其他目標造成的，則若為攻擊附帶能力，則持續一次攻擊，若為其他特殊能力，則持續到該目標回合結束後結束。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CW58">
       <text>
-        <t xml:space="preserve">全力防御
-这是一个标准动作。
-你尽全力躲闪你的敌人。
-你原本的基础防御翻倍，并且若受到的攻击为范围攻击并且允许躲避，那么用于抵消范围伤害或者范围效果的相关检定结果中的所有成功数翻倍（包括自然成功数和附加成功数），持续至你的下回合开始时。
-特殊：本能力与反射动作离开攻击范围带来的好处无法互相叠加。
-特殊说明：当你进行全力防御时，你计算当前的基础防御，根据该值计算翻倍后的基础防御。
-（如你当前基础防御为5，你进行全力防御为10，然后目标的攻击拥有高速优势3，则你的基础防御为7）
-（如你当前基础防御为5，你进行全力防御为10，然后因不良状态点数基础防御承受3点减值，则你的基础防御为7）</t>
+        <t xml:space="preserve">全力防禦
+這是一個標準動作。
+你盡全力躲閃你的敵人。
+你原本的基礎防禦翻倍，並且若受到的攻擊為範圍攻擊並且允許躲避，那麼用於抵消範圍傷害或者範圍效果的相關檢定結果中的所有成功數翻倍（包括自然成功數和附加成功數），持續至你的下回合開始時。
+特殊：本能力與反射動作離開攻擊範圍帶來的好處無法互相疊加。
+特殊說明：當你進行全力防禦時，你計算當前的基礎防禦，根據該值計算翻倍後的基礎防禦。
+（如你當前基礎防禦為5，你進行全力防禦為10，然後目標的攻擊擁有高速優勢3，則你的基礎防禦為7）
+（如你當前基礎防禦為5，你進行全力防禦為10，然後因不良狀態點數基礎防禦承受3點減值，則你的基礎防禦為7）</t>
       </text>
     </comment>
     <comment authorId="0" ref="C53">
@@ -326,77 +326,77 @@
     </comment>
     <comment authorId="0" ref="C20">
       <text>
-        <t xml:space="preserve">身体的健康程度和抵抗力、新陈代谢的活跃度等，抵挡伤病的能力。
-任何活着的东西都拥有耐力值。
-耐力为0的人物会直接死亡。</t>
+        <t xml:space="preserve">身體的健康程度和抵抗力、新陳代謝的活躍度等，抵擋傷病的能力。
+任何活著的東西都擁有耐力值。
+耐力為0的人物會直接死亡。</t>
       </text>
     </comment>
     <comment authorId="0" ref="DA58">
       <text>
-        <t xml:space="preserve">肉搏格挡
-这是一个移动动作。
-你必须拥有对应的肢体才可以格挡（如胳膊，腿，尾巴之类）
-你的防御获得相当于你肉搏技能等级的格挡防御，持续至你的下回合开始时。
-白刃格挡
-这是一个移动动作。
-你必须持有一件白刃武器才可以进行格挡。
-你的防御获得相当于你白刃技能等级的格挡防御，持续至你的下回合开始时。</t>
+        <t xml:space="preserve">肉搏格擋
+這是一個移動動作。
+你必須擁有對應的肢體才可以格擋（如胳膊，腿，尾巴之類）
+你的防禦獲得相當於你肉搏技能等級的格擋防禦，持續至你的下回合開始時。
+白刃格擋
+這是一個移動動作。
+你必須持有一件白刃武器才可以進行格擋。
+你的防禦獲得相當於你白刃技能等級的格擋防禦，持續至你的下回合開始時。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI43">
       <text>
-        <t xml:space="preserve">意志豁免：有些场合中会使用意志豁免检定，即此项，常用于抵御心灵影响或精神伤害，意志豁免检定的初始DP等于决心+感受（自我保护）</t>
+        <t xml:space="preserve">意志豁免：有些場合中會使用意志豁免檢定，即此項，常用於抵禦心靈影響或精神傷害，意志豁免檢定的初始DP等於決心+感受（自我保護）</t>
       </text>
     </comment>
     <comment authorId="0" ref="BQ51">
       <text>
-        <t xml:space="preserve">解除：解除三阶本能觉醒是一个自由动作。注意你会直接解除所有本能觉醒，而不是退回二阶或者一阶。</t>
+        <t xml:space="preserve">解除：解除三階本能覺醒是一個自由動作。注意你會直接解除所有本能覺醒，而不是退回二階或者一階。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B144">
       <text>
-        <t xml:space="preserve">道具：特殊的装备位，一般是可以拿出来单独使用的，若没有特殊说明，需要一只保持空出一只手来持握该道具。
-武器：特殊的装备位，若没有特殊说明，需要一只保持空出一只手来持握该武器。
-盾牌：特殊的装备位，若没有特殊说明，需要一只保持空出一只手来持握该盾牌。
-除了武器，盾牌，戒指，盔甲，插件，可搭载的装置，道具以外，其余所有的装备穿脱都需要一个标准动作。
-当插件或者可搭载的装备被脱下来后，这些装备也被视为一起脱了下来。</t>
+        <t xml:space="preserve">道具：特殊的裝備位，一般是可以拿出來單獨使用的，若沒有特殊說明，需要一隻保持空出一隻手來持握該道具。
+武器：特殊的裝備位，若沒有特殊說明，需要一隻保持空出一隻手來持握該武器。
+盾牌：特殊的裝備位，若沒有特殊說明，需要一隻保持空出一隻手來持握該盾牌。
+除了武器，盾牌，戒指，盔甲，插件，可搭載的裝置，道具以外，其餘所有的裝備穿脫都需要一個標準動作。
+當插件或者可搭載的裝備被脫下來後，這些裝備也被視為一起脫了下來。</t>
       </text>
     </comment>
     <comment authorId="0" ref="DE58">
       <text>
         <t xml:space="preserve">掩蔽：
-寻求掩蔽是一种有效的防御行为。
-在战斗中，人物可以利用自己可以搬动或移动的物品架在身前，或者躲在树木，墙壁的后面，也可以由于烟雾，云层的效果形成掩蔽。
-一方面可以用来躲藏（这种情况下一般障碍物要求比角色体型要大），一方面可以有效避免遭受攻击，躲避远程攻击尤其有效。
-当然人物也可以自己搬动或拾取物品架在身前，形成掩蔽（拾取物品是一个移动动作）。若人物可以拿动掩蔽物，且他在这一轮中还可以进行移动（例如某种使用迅捷动作移动的能力，或利用标准动作移动），他可以在掩蔽的情况下带着物品移动。 
-特殊：当目标拥有绕过全掩蔽定位你和攻击你的能力，则不视为你全掩蔽。如范围攻击，或者雷达定位配合【贯穿】攻击，在击破你的掩蔽物后会对你造成伤害。
-掩蔽分为部分掩蔽和全掩蔽状态。
-两个目标所处格子的任意一点进行连线，若有障碍物，则视为部分掩蔽。若找不到没有障碍物的两点连线，则视为全掩蔽。
-所以一般情况下，掩蔽都具备方向性，也就是只针对某一方向具备掩蔽。
-处于部分掩蔽下，则针对双方的单体攻击时，自身获得4点掩蔽防御。
-处于全掩蔽下，则双方无法进行攻击，称之为没有视野线和效果线。</t>
+尋求掩蔽是一種有效的防禦行為。
+在戰鬥中，人物可以利用自己可以搬動或移動的物品架在身前，或者躲在樹木，牆壁的後面，也可以由於煙霧，雲層的效果形成掩蔽。
+一方面可以用來躲藏（這種情況下一般障礙物要求比角色體型要大），一方面可以有效避免遭受攻擊，躲避遠程攻擊尤其有效。
+當然人物也可以自己搬動或拾取物品架在身前，形成掩蔽（拾取物品是一個移動動作）。若人物可以拿動掩蔽物，且他在這一輪中還可以進行移動（例如某種使用迅捷動作移動的能力，或利用標準動作移動），他可以在掩蔽的情況下帶著物品移動。 
+特殊：當目標擁有繞過全掩蔽定位你和攻擊你的能力，則不視為你全掩蔽。如範圍攻擊，或者雷達定位配合【貫穿】攻擊，在擊破你的掩蔽物後會對你造成傷害。
+掩蔽分為部分掩蔽和全掩蔽狀態。
+兩個目標所處格子的任意一點進行連線，若有障礙物，則視為部分掩蔽。若找不到沒有障礙物的兩點連線，則視為全掩蔽。
+所以一般情況下，掩蔽都具備方向性，也就是隻針對某一方向具備掩蔽。
+處於部分掩蔽下，則針對雙方的單體攻擊時，自身獲得4點掩蔽防禦。
+處於全掩蔽下，則雙方無法進行攻擊，稱之為沒有視野線和效果線。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B111">
       <text>
-        <t xml:space="preserve">手表插件——书签
-本质：特异本质
-价格：200分
-分类：手表插件
-效果：购买本插件后，你将获得一页技能仓库。
-你可以往技能仓库里面任意储存支线和分数，然后在技能仓库里面进行整备资源。
-每次短休结束后，你可以重新使用仓库中的支线和分数购买仓库里的资源。
-仓库中只能储存技能，法术，招式等所有处于技能树或者施法表或者单独技艺中需要主动开启的能力。血统，改造，称号，流派，修炼体系等主干中的主动开启能力无法被储存。
-每一页只能储存一个技能，并且无法改变。
-书签在有需求时也可以进行快速整备，但是当你如此做时，你需要支付一个完整的回合和（你准备进行更换的技能数量+本场冒险世界下已进行快速整备的次数）*1点意志力。</t>
+        <t xml:space="preserve">手錶插件——書籤
+本質：特異本質
+價格：200分
+分類：手錶插件
+效果：購買本插件後，你將獲得一頁技能倉庫。
+你可以往技能倉庫裡面任意儲存支線和分數，然後在技能倉庫裡面進行整備資源。
+每次短休結束後，你可以重新使用倉庫中的支線和分數購買倉庫裡的資源。
+倉庫中只能儲存技能，法術，招式等所有處於技能樹或者施法表或者單獨技藝中需要主動開啟的能力。血統，改造，稱號，流派，修煉體系等主幹中的主動開啟能力無法被儲存。
+每一頁只能儲存一個技能，並且無法改變。
+書籤在有需求時也可以進行快速整備，但是當你如此做時，你需要支付一個完整的回合和（你準備進行更換的技能數量+本場冒險世界下已進行快速整備的次數）*1點意志力。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Y3">
       <text>
-        <t xml:space="preserve">人物的生命值，其为0到其生命值上限的任何数值。
-生物的每1点生命值有4种伤势状态，分别是“完好”，“冲击伤害（简写为B）”，“严重伤害（简写为L）”，“恶性伤害（简写为A）”。
-随着一个生物受伤和接受治疗，其生命值状态也会出现频繁的波动。
-若没有特殊说明，当一个生物生命值的全部转为恶性伤害时，该生物死亡。</t>
+        <t xml:space="preserve">人物的生命值，其為0到其生命值上限的任何數值。
+生物的每1點生命值有4種傷勢狀態，分別是“完好”，“衝擊傷害（簡寫為B）”，“嚴重傷害（簡寫為L）”，“惡性傷害（簡寫為A）”。
+隨著一個生物受傷和接受治療，其生命值狀態也會出現頻繁的波動。
+若沒有特殊說明，當一個生物生命值的全部轉為惡性傷害時，該生物死亡。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C45">
@@ -412,29 +412,29 @@
     </comment>
     <comment authorId="0" ref="BI35">
       <text>
-        <t xml:space="preserve">先攻：用于决定战斗中的行动顺序，初始值为敏捷+沉着。
+        <t xml:space="preserve">先攻：用於決定戰鬥中的行動順序，初始值為敏捷+沉著。
 </t>
       </text>
     </comment>
     <comment authorId="0" ref="CO67">
       <text>
-        <t xml:space="preserve">力场加值：
-力场防御一般加在防御或某种检定上，它意味着有一个力场效果正在辅助你的某一方面。
-力场加值不会叠加。
-力场加值可以从任何途径获得，所以获得该加值时，需要支付额外特性。</t>
+        <t xml:space="preserve">力場加值：
+力場防禦一般加在防禦或某種檢定上，它意味著有一個力場效果正在輔助你的某一方面。
+力場加值不會疊加。
+力場加值可以從任何途徑獲得，所以獲得該加值時，需要支付額外特性。</t>
       </text>
     </comment>
     <comment authorId="0" ref="H78">
       <text>
-        <t xml:space="preserve">血统
-模板之一，无论如何，角色只能获得一个血统。
-血统是一种来自传承的力量，只要拥有某种血统，无论其天赋如何，是否经过后天努力，其基本特性都很难有所变化。
-所有兑换了血统的单位在判定上都视为超自然生物，除非血统本身有说明。</t>
+        <t xml:space="preserve">血統
+模板之一，無論如何，角色只能獲得一個血統。
+血統是一種來自傳承的力量，只要擁有某種血統，無論其天賦如何，是否經過後天努力，其基本特性都很難有所變化。
+所有兌換了血統的單位在判定上都視為超自然生物，除非血統本身有說明。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B136">
       <text>
-        <t xml:space="preserve">护腕（护臂）：带在上臂的装备，一般为魔幻本质特有，每个角色只有一个护腕位。</t>
+        <t xml:space="preserve">護腕（護臂）：帶在上臂的裝備，一般為魔幻本質特有，每個角色只有一個護腕位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C37">
@@ -452,74 +452,74 @@
     <comment authorId="0" ref="CT67">
       <text>
         <t xml:space="preserve">偏斜加值：
-偏斜防御一般加在攻击，防御和对抗范围效果的检定上，它意味着攻击或敌意物质会部分地与你的身体错开，这有可能是因为你的身体并不在它看起来的位置，也可能是空间扭曲。
-偏斜加值不会叠加。
-偏斜加值可以从任何途径获得，所以获得该加值时，需要支付额外特性。</t>
+偏斜防禦一般加在攻擊，防禦和對抗範圍效果的檢定上，它意味著攻擊或敵意物質會部分地與你的身體錯開，這有可能是因為你的身體並不在它看起來的位置，也可能是空間扭曲。
+偏斜加值不會疊加。
+偏斜加值可以從任何途徑獲得，所以獲得該加值時，需要支付額外特性。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AJ3">
       <text>
-        <t xml:space="preserve">当人物受到伤害时，先减少对应的完好生命值，然后将当前所受伤害加在之前的所受的对应伤害上。
-然后将当前所有的伤害相加（所受冲击伤害+所受严重伤害+所受恶性伤害）是否大于目标的生命值上限：
-若小于，则意味着目标还有完好生命值。
-若等于，则意味着目标没有完好生命值了，但是无需转化伤势。
-若大于，则意味着目标不仅没有完好生命值，且需要转化伤势。
-此时按照2点冲击伤害：1点严重伤害，2点严重伤害：1点恶性伤害向下转换。
-直至所有的伤害相加等于目标的生命值上限为止。
-当人物转化结束后，若其生命值状态全部为恶性伤害，则总和等于或大于生命值上限，则人物死亡。
-当人物同时受到多种不同程度的伤害时，从程度最低的开始计算。</t>
+        <t xml:space="preserve">當人物受到傷害時，先減少對應的完好生命值，然後將當前所受傷害加在之前的所受的對應傷害上。
+然後將當前所有的傷害相加（所受衝擊傷害+所受嚴重傷害+所受惡性傷害）是否大於目標的生命值上限：
+若小於，則意味著目標還有完好生命值。
+若等於，則意味著目標沒有完好生命值了，但是無需轉化傷勢。
+若大於，則意味著目標不僅沒有完好生命值，且需要轉化傷勢。
+此時按照2點衝擊傷害：1點嚴重傷害，2點嚴重傷害：1點惡性傷害向下轉換。
+直至所有的傷害相加等於目標的生命值上限為止。
+當人物轉化結束後，若其生命值狀態全部為惡性傷害，則總和等於或大於生命值上限，則人物死亡。
+當人物同時受到多種不同程度的傷害時，從程度最低的開始計算。</t>
       </text>
     </comment>
     <comment authorId="0" ref="O78">
       <text>
         <t xml:space="preserve">改造
-模板之一，无论如何，角色只能获得一个改造。
-改造的力量源于形体外在或内在的转化，个人的天赋与努力对其基本特性没有太大影响。
-所有兑换了改造的单位在判定上都视为超自然生物，除非改造本身有说明。</t>
+模板之一，無論如何，角色只能獲得一個改造。
+改造的力量源於形體外在或內在的轉化，個人的天賦與努力對其基本特性沒有太大影響。
+所有兌換了改造的單位在判定上都視為超自然生物，除非改造本身有說明。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Q144">
       <text>
-        <t xml:space="preserve">道具：特殊的装备位，一般是可以拿出来单独使用的，若没有特殊说明，需要一只保持空出一只手来持握该道具。
-武器：特殊的装备位，若没有特殊说明，需要一只保持空出一只手来持握该武器。
-盾牌：特殊的装备位，若没有特殊说明，需要一只保持空出一只手来持握该盾牌。
-除了武器，盾牌，戒指，盔甲，插件，可搭载的装置，道具以外，其余所有的装备穿脱都需要一个标准动作。
-当插件或者可搭载的装备被脱下来后，这些装备也被视为一起脱了下来。</t>
+        <t xml:space="preserve">道具：特殊的裝備位，一般是可以拿出來單獨使用的，若沒有特殊說明，需要一隻保持空出一隻手來持握該道具。
+武器：特殊的裝備位，若沒有特殊說明，需要一隻保持空出一隻手來持握該武器。
+盾牌：特殊的裝備位，若沒有特殊說明，需要一隻保持空出一隻手來持握該盾牌。
+除了武器，盾牌，戒指，盔甲，插件，可搭載的裝置，道具以外，其餘所有的裝備穿脫都需要一個標準動作。
+當插件或者可搭載的裝備被脫下來後，這些裝備也被視為一起脫了下來。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AM36">
       <text>
-        <t xml:space="preserve">本技能可以帮助角色得知敌人的信息。
-动作：一般情况下，知识检定无需动作。
-使用：角色可以在战斗中通过学识技能来辨识敌人的大致信息。
-若如此做，DC等于敌人支线等级的平方（D1,C2,B3,A4,S5,SS6）
-PC检定成功时，获取第一个信息。
-检定成功数每多出一倍DC，则可以获取下一个信息。
-敌人信息获取顺序如下：
-1.【概念段】包括体型、先攻、触及、战斗速度、描述等
-2.【属性段】
+        <t xml:space="preserve">本技能可以幫助角色得知敵人的信息。
+動作：一般情況下，知識檢定無需動作。
+使用：角色可以在戰鬥中通過學識技能來辨識敵人的大致信息。
+若如此做，DC等於敵人支線等級的平方（D1,C2,B3,A4,S5,SS6）
+PC檢定成功時，獲取第一個信息。
+檢定成功數每多出一倍DC，則可以獲取下一個信息。
+敵人信息獲取順序如下：
+1.【概念段】包括體型、先攻、觸及、戰鬥速度、描述等
+2.【屬性段】
 3.【技能段】
-4.【攻击能力段】&amp;【防御能力段】
+4.【攻擊能力段】&amp;【防禦能力段】
 5.【特殊能力段】
-如：C级怪物，检定成功数为10，则基础DC为4，多出来6点，也就是可以再得知3个信息。
-注：并非所有敌人都有信息，普通怪物很可能省略属性段和技能段。</t>
+如：C級怪物，檢定成功數為10，則基礎DC為4，多出來6點，也就是可以再得知3個信息。
+注：並非所有敵人都有信息，普通怪物很可能省略屬性段和技能段。</t>
       </text>
     </comment>
     <comment authorId="0" ref="X20">
       <text>
-        <t xml:space="preserve">在耐力相关的检定上获得n个附加成功。
-生命值额外增加n(n+1)/2点。
+        <t xml:space="preserve">在耐力相關的檢定上獲得n個附加成功。
+生命值額外增加n(n+1)/2點。
 角色可以2^(n-1)周不吃不喝不睡。
-闭气时间2^n倍。
-强韧豁免检定获得n*3DP完美加值。</t>
+閉氣時間2^n倍。
+強韌豁免檢定獲得n*3DP完美加值。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CY67">
       <text>
         <t xml:space="preserve">洞察加值：
-洞察加值一般加在防御或某种检定上，它意味着你拥有卓越的观察力，可以看透困难之所在并加以避免。
-洞察加值不会叠加，但是洞察减值可以无限叠加。
-洞察加值一般由瞳术带来。</t>
+洞察加值一般加在防禦或某種檢定上，它意味著你擁有卓越的觀察力，可以看透困難之所在並加以避免。
+洞察加值不會疊加，但是洞察減值可以無限疊加。
+洞察加值一般由瞳術帶來。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BS2">
@@ -530,45 +530,45 @@
     </comment>
     <comment authorId="0" ref="BU2">
       <text>
-        <t xml:space="preserve">你可以在建立人物卡时选择一些缺陷，以此来让你的人物更加栩栩如生。
-每个缺陷会提供如同其等级的缺陷点数。为了直观感受，缺陷的等级用负数来表示，但在考虑缺陷点数时，用正数来理解。
-每2个缺陷点数可以兑换1个天赋点数，你可以使用这个天赋点数去获得天赋，规则如同专长一般。
--1级的缺陷获得1点缺陷点数，-2级的缺陷获得2点缺陷点数，-1~-2级的缺陷获得3点缺陷点数。
-注：所有缺陷无法通过让轮回之境修复身体或肢体来进行消除，有些可以自行消除的缺陷会自行说明。</t>
+        <t xml:space="preserve">你可以在建立人物卡時選擇一些缺陷，以此來讓你的人物更加栩栩如生。
+每個缺陷會提供如同其等級的缺陷點數。為了直觀感受，缺陷的等級用負數來表示，但在考慮缺陷點數時，用正數來理解。
+每2個缺陷點數可以兌換1個天賦點數，你可以使用這個天賦點數去獲得天賦，規則如同專長一般。
+-1級的缺陷獲得1點缺陷點數，-2級的缺陷獲得2點缺陷點數，-1~-2級的缺陷獲得3點缺陷點數。
+注：所有缺陷無法通過讓輪迴之境修復身體或肢體來進行消除，有些可以自行消除的缺陷會自行說明。</t>
       </text>
     </comment>
     <comment authorId="0" ref="V78">
       <text>
-        <t xml:space="preserve">瞳术
-模板之一，若没有特殊说明，角色只能获得一个瞳术。
-瞳术是一种特殊的能力，可以理解为针对眼球进行的改造。
-所有兑换了瞳术的单位在判定上都视为超自然生物，除非瞳术本身有说明。</t>
+        <t xml:space="preserve">瞳術
+模板之一，若沒有特殊說明，角色只能獲得一個瞳術。
+瞳術是一種特殊的能力，可以理解為針對眼球進行的改造。
+所有兌換了瞳術的單位在判定上都視為超自然生物，除非瞳術本身有說明。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI52">
       <text>
-        <t xml:space="preserve">四阶本能觉醒：
-本能觉醒的第四阶段开始是真正开始向天地大道进发，开始可以精确的对能量进行控制和操控，并调整自己的基因，从而使自己面对任何情况。</t>
+        <t xml:space="preserve">四階本能覺醒：
+本能覺醒的第四階段開始是真正開始向天地大道進發，開始可以精確的對能量進行控制和操控，並調整自己的基因，從而使自己面對任何情況。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Q136">
       <text>
-        <t xml:space="preserve">手套：戴在手上的装备，每个角色只有一个手套位。</t>
+        <t xml:space="preserve">手套：戴在手上的裝備，每個角色只有一個手套位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AT3">
       <text>
-        <t xml:space="preserve">当人物因伤势过重而昏迷时，可以花费1点意志力使昏迷延后。
-若为战斗时，则每1点意志力可以使人物继续行动1轮，每轮结束时决定是否花费该意志力，若不花费，则该轮结束后立即昏迷。
-若为非战斗时，则每1点意志力可以使人物继续行动1分钟。
-在持续时间内，人物不会因为伤势过重而昏迷。
-除非有特殊说明，否则人物无法在进行周期性（行为）检定时，使用意志力。
-需要注意的是，人物只有在保有自我意识的情况下可以使用意志力。换言之，处于睡眠、昏迷等类似不良状态时，无法使用意志力。</t>
+        <t xml:space="preserve">當人物因傷勢過重而昏迷時，可以花費1點意志力使昏迷延後。
+若為戰鬥時，則每1點意志力可以使人物繼續行動1輪，每輪結束時決定是否花費該意志力，若不花費，則該輪結束後立即昏迷。
+若為非戰鬥時，則每1點意志力可以使人物繼續行動1分鐘。
+在持續時間內，人物不會因為傷勢過重而昏迷。
+除非有特殊說明，否則人物無法在進行週期性（行為）檢定時，使用意志力。
+需要注意的是，人物只有在保有自我意識的情況下可以使用意志力。換言之，處於睡眠、昏迷等類似不良狀態時，無法使用意志力。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BK52">
       <text>
-        <t xml:space="preserve">被动开启：当你累计为三阶本能觉醒投入了42XP之后，则你上文所述的危急关头，可以获得一次提升本能觉醒层级的机会。你投掷一个4D10，若结果在36或36以上，则你成功开启了四阶本能觉醒。</t>
+        <t xml:space="preserve">被動開啟：當你累計為三階本能覺醒投入了42XP之後，則你上文所述的危急關頭，可以獲得一次提升本能覺醒層級的機會。你投擲一個4D10，若結果在36或36以上，則你成功開啟了四階本能覺醒。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C54">
@@ -584,49 +584,49 @@
     </comment>
     <comment authorId="0" ref="C21">
       <text>
-        <t xml:space="preserve">逻辑思维的能力、自主意识，自主行动能力，计算能力、分析能力和记忆力等，有时也代表了人物对超自然能量的分配和控制。
-任何能够以一套行为逻辑进行行动的存在都拥有智力值。
-智力为0的人物失去自主行动能力。他将会处于“昏迷”状态。</t>
+        <t xml:space="preserve">邏輯思維的能力、自主意識，自主行動能力，計算能力、分析能力和記憶力等，有時也代表了人物對超自然能量的分配和控制。
+任何能夠以一套行為邏輯進行行動的存在都擁有智力值。
+智力為0的人物失去自主行動能力。他將會處於“昏迷”狀態。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BN52">
       <text>
-        <t xml:space="preserve">主动开启：若你处于三阶本能觉醒的状态，你可以通过一个迅捷动作，并且支付1点意志力来开启四阶本能觉醒。</t>
+        <t xml:space="preserve">主動開啟：若你處於三階本能覺醒的狀態，你可以通過一個迅捷動作，並且支付1點意志力來開啟四階本能覺醒。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AC78">
       <text>
-        <t xml:space="preserve">修炼体系
-模板之一，若没有特殊说明，角色只能获得一个修炼体系。
-修炼体系包括东方的修真功法和西方的一些修炼方式。
-为了防止爆体而亡，每个人只能修习一种修炼方式。修炼一般会为人物带来各种被动效果，并且可以在各种程度上增幅人物的能力。
-所有兑换了修炼体系的单位在判定上都视为超自然生物，除非该修炼体系本身有说明。</t>
+        <t xml:space="preserve">修煉體系
+模板之一，若沒有特殊說明，角色只能獲得一個修煉體系。
+修煉體系包括東方的修真功法和西方的一些修煉方式。
+為了防止爆體而亡，每個人只能修習一種修煉方式。修煉一般會為人物帶來各種被動效果，並且可以在各種程度上增幅人物的能力。
+所有兌換了修煉體系的單位在判定上都視為超自然生物，除非該修煉體系本身有說明。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI44">
       <text>
-        <t xml:space="preserve">反射豁免：有些场合中会使用反射豁免检定，即此项，常用于回避范围攻击，反射豁免检定的初始DP等于敏捷+运动（自我保护）。</t>
+        <t xml:space="preserve">反射豁免：有些場合中會使用反射豁免檢定，即此項，常用於迴避範圍攻擊，反射豁免檢定的初始DP等於敏捷+運動（自我保護）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BQ52">
       <text>
-        <t xml:space="preserve">解除：你可以用一个自由动作解除全部本能觉醒。你不可以从某个高阶本能觉醒退回某个低阶本能觉醒状态。</t>
+        <t xml:space="preserve">解除：你可以用一個自由動作解除全部本能覺醒。你不可以從某個高階本能覺醒退回某個低階本能覺醒狀態。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BB3">
       <text>
-        <t xml:space="preserve">每进行一次至少1小时的短休息（不能做其他行动），恢复1点意志力。
-每进行至少8小时的长休息（不进行任何行动，而是用于睡眠之类），人物可以投掷1D10，这不是一次检定，恢复该投骰结果+传奇决心+传奇沉着/点意志力。</t>
+        <t xml:space="preserve">每進行一次至少1小時的短休息（不能做其他行動），恢復1點意志力。
+每進行至少8小時的長休息（不進行任何行動，而是用於睡眠之類），人物可以投擲1D10，這不是一次檢定，恢復該投骰結果+傳奇決心+傳奇沉著/點意志力。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BS52">
       <text>
-        <t xml:space="preserve">效果：当你处于解开四阶本能觉醒状态时，你保留一、二、三阶本能觉醒带来的效果。在此之外，你获得如下两种能力：
-自身基因控制：你可以以一个自由动作，消耗X点意志力，或者调整自己的属性值，选择一个属性获得X点完美加值，另一个属性受到X点完美减值。
-你只能使用本方法调整自己属性中基本属性，你最多使一个属性获得的完美加值不能超过其原本的基本属性（如原本的基本属性为6，则最多再获得6点），你使另外一个属性受到的减值，最多不能超过其基本属性的一半（如原本的基本属性为6，则最多降低为3点）。
-入微：这个能力体现在对能量的控制上，大致同样有两种用法，控制自己的能量和引导他人的能量。
-当你使用消耗能量的能力时，若该能力可以增幅，每增幅1点能量视为2点能量，但仍然只占用1点增幅上限。
-当有人对你使用消耗能量的能力时，你自动得知他所使用的能量以及消耗数量，如果他所使用的能力投入了基本消耗外的额外能量增幅，该额外增幅的部分对你无效。</t>
+        <t xml:space="preserve">效果：當你處於解開四階本能覺醒狀態時，你保留一、二、三階本能覺醒帶來的效果。在此之外，你獲得如下兩種能力：
+自身基因控制：你可以以一個自由動作，消耗X點意志力，或者調整自己的屬性值，選擇一個屬性獲得X點完美加值，另一個屬性受到X點完美減值。
+你只能使用本方法調整自己屬性中基本屬性，你最多使一個屬性獲得的完美加值不能超過其原本的基本屬性（如原本的基本屬性為6，則最多再獲得6點），你使另外一個屬性受到的減值，最多不能超過其基本屬性的一半（如原本的基本屬性為6，則最多降低為3點）。
+入微：這個能力體現在對能量的控制上，大致同樣有兩種用法，控制自己的能量和引導他人的能量。
+當你使用消耗能量的能力時，若該能力可以增幅，每增幅1點能量視為2點能量，但仍然只佔用1點增幅上限。
+當有人對你使用消耗能量的能力時，你自動得知他所使用的能量以及消耗數量，如果他所使用的能力投入了基本消耗外的額外能量增幅，該額外增幅的部分對你無效。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C46">
@@ -648,29 +648,29 @@
     <comment authorId="0" ref="AJ78">
       <text>
         <t xml:space="preserve">典籍
-模板之一，若没有特殊说明，角色只能获得一本典籍。
-在东西方世界中，修炼各种奇妙的功法都需要一本魔法书或者武功秘籍。
-而有一部分典籍经过长年累月的积累，它们苏醒了自己的意识，觉醒了自己的力量。而每个典籍的性格又各不相同，他们会互相排斥。
-所有兑换了典籍的单位在判定上都视为超自然生物，除非典籍本身有说明。</t>
+模板之一，若沒有特殊說明，角色只能獲得一本典籍。
+在東西方世界中，修煉各種奇妙的功法都需要一本魔法書或者武功秘籍。
+而有一部分典籍經過長年累月的積累，它們甦醒了自己的意識，覺醒了自己的力量。而每個典籍的性格又各不相同，他們會互相排斥。
+所有兌換了典籍的單位在判定上都視為超自然生物，除非典籍本身有說明。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BX52">
       <text>
-        <t xml:space="preserve">持续时间：需要注意的是，开启四阶本能觉醒必须在开启三阶本能觉醒的前提下，同时解除三阶本能觉醒会自动解除所有本能觉醒，所以四阶没有额外的能耗（一阶每轮消耗1点意志力代为支付）。</t>
+        <t xml:space="preserve">持續時間：需要注意的是，開啟四階本能覺醒必須在開啟三階本能覺醒的前提下，同時解除三階本能覺醒會自動解除所有本能覺醒，所以四階沒有額外的能耗（一階每輪消耗1點意志力代為支付）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI36">
       <text>
-        <t xml:space="preserve">基础防御：用于决定人物的防御值，初始值为敏捷和感知中较低者。基础防御是可以与其他能力带来的基础防御叠加的。
+        <t xml:space="preserve">基礎防禦：用於決定人物的防禦值，初始值為敏捷和感知中較低者。基礎防禦是可以與其他能力帶來的基礎防禦疊加的。
 </t>
       </text>
     </comment>
     <comment authorId="0" ref="BJ3">
       <text>
         <t xml:space="preserve">意志力的基本用法：
-人物在进行一个行动时（无论回合外还是回合内），若该行动不是周期性行为且只需一次检定（包括并不限于攻击、技能判定、对抗、防御等）可以无需任何动作直接支付1点意志力，在该行动上获得3DP的完美加值，这种用法对一次行动只能使用一次。
-或者人物在受到攻击时，可以支付1点意志力，针对该次攻击人物在防御上获得3点完美加值。
-有些能力可以增加意志力的基本用法带来的加值。</t>
+人物在進行一個行動時（無論回合外還是回合內），若該行動不是週期性行為且只需一次檢定（包括並不限於攻擊、技能判定、對抗、防禦等）可以無需任何動作直接支付1點意志力，在該行動上獲得3DP的完美加值，這種用法對一次行動只能使用一次。
+或者人物在受到攻擊時，可以支付1點意志力，針對該次攻擊人物在防禦上獲得3點完美加值。
+有些能力可以增加意志力的基本用法帶來的加值。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CO2">
@@ -680,13 +680,13 @@
     </comment>
     <comment authorId="0" ref="B38">
       <text>
-        <t xml:space="preserve">心智系技能：心智系技能是纯粹的知识和技巧，如果心智技能为0，你无法进行对应的检定，视为检定结果自动失败。</t>
+        <t xml:space="preserve">心智系技能：心智系技能是純粹的知識和技巧，如果心智技能為0，你無法進行對應的檢定，視為檢定結果自動失敗。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CQ2">
       <text>
-        <t xml:space="preserve">不同于一般的凡人，你可能拥有一些很特别的才能。
-天赋是通过的缺陷获得的，每2个缺陷点数可以兑换1个天赋点数，你可以使用这个天赋点数去获得天赋，规则如同专长一般。</t>
+        <t xml:space="preserve">不同於一般的凡人，你可能擁有一些很特別的才能。
+天賦是通過的缺陷獲得的，每2個缺陷點數可以兌換1個天賦點數，你可以使用這個天賦點數去獲得天賦，規則如同專長一般。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C38">
@@ -702,9 +702,9 @@
     </comment>
     <comment authorId="0" ref="AT78">
       <text>
-        <t xml:space="preserve">称号与流派
-称号与流派是一种经过系统的训练而能掌握的技能体系，只要能够完成同样的训练，其收获也应当相同，如果没有特殊说明，一般不具备排他性。称号与流派的技能是一系列独特的能力技能树，附带一些专有的技艺技巧，它的撰写规范通常和普通的能力相近，但自成系统，可以不断地成长。
-同一个称号和流派无法反复购买，这也包括在同一个总纲下的分支，若已经购买了其中一个分支，则无法购买另外的分支。</t>
+        <t xml:space="preserve">稱號與流派
+稱號與流派是一種經過系統的訓練而能掌握的技能體系，只要能夠完成同樣的訓練，其收穫也應當相同，如果沒有特殊說明，一般不具備排他性。稱號與流派的技能是一系列獨特的能力技能樹，附帶一些專有的技藝技巧，它的撰寫規範通常和普通的能力相近，但自成系統，可以不斷地成長。
+同一個稱號和流派無法反覆購買，這也包括在同一個總綱下的分支，若已經購買了其中一個分支，則無法購買另外的分支。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Z153">
@@ -714,13 +714,13 @@
     </comment>
     <comment authorId="0" ref="X21">
       <text>
-        <t xml:space="preserve">在智力相关的检定上获得n个附加成功。
-在每次影片结束结算经验时，你根据本场恐怖片中你最低的传奇智力数获得额外的4*n点经验红利，任何情况下，红利无法产生红利。</t>
+        <t xml:space="preserve">在智力相關的檢定上獲得n個附加成功。
+在每次影片結束結算經驗時，你根據本場恐怖片中你最低的傳奇智力數獲得額外的4*n點經驗紅利，任何情況下，紅利無法產生紅利。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B30">
       <text>
-        <t xml:space="preserve">生理系技能：生理系技能不完全是纯粹的技巧，许多技巧即使没有知识，单靠自身的素质也可以进行尝试，如果生理技能为0，你仍然可以尝试进行检定，但是会失去一个自然成功数。</t>
+        <t xml:space="preserve">生理系技能：生理系技能不完全是純粹的技巧，許多技巧即使沒有知識，單靠自身的素質也可以進行嘗試，如果生理技能為0，你仍然可以嘗試進行檢定，但是會失去一個自然成功數。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C30">
@@ -736,45 +736,45 @@
     </comment>
     <comment authorId="0" ref="BI53">
       <text>
-        <t xml:space="preserve">五阶本能觉醒： 
-本能觉醒第五阶能力是控制能量，即所谓大道层次，人物获得“圣位”。
-本质上，圣位是有限的，生物只有在剧情中获得圣位才行，也就是获得相应的神域或道，最简单直接的方式就是弑神或者击杀其他五阶强者，通过神格吸收那个神的神域。
-注意，虽然有许多能力提供神格让你能够容纳圣位，但没有五阶本能觉醒，即便你拥有极高的神格也不会开启第五阶，因为你对这样的力量空能运用却缺乏理解。</t>
+        <t xml:space="preserve">五階本能覺醒： 
+本能覺醒第五階能力是控制能量，即所謂大道層次，人物獲得“聖位”。
+本質上，聖位是有限的，生物只有在劇情中獲得聖位才行，也就是獲得相應的神域或道，最簡單直接的方式就是弒神或者擊殺其他五階強者，通過神格吸收那個神的神域。
+注意，雖然有許多能力提供神格讓你能夠容納聖位，但沒有五階本能覺醒，即便你擁有極高的神格也不會開啟第五階，因為你對這樣的力量空能運用卻缺乏理解。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BK53">
       <text>
-        <t xml:space="preserve">主动开启：四阶本能觉醒开启之后，且度过了两个冒险世界（包括开启四阶的那场）之后，你可以选择挑战心魔。当你战胜自己的心魔之后，你可以跨入5阶本能觉醒。
-每场冒险世界，你只能挑战一次心魔。
-挑战心魔时你进入你自身的心灵幻境中，但外界时间同步流逝，你在幻境中经过多久时间，外界也会经过同样的时间，在战斗中触发会是极端危险的状况，此时针对外界而言，你无法控制你的角色，但是你可以依本能行动。
-这种凶险的形式对各人表现不一，通常心魔本身和度过的方法联系人物的扮演，个性与背景。具体的表现形式和通过判断由ST掌握。ST可以为角色设计独立故事，源于其故事中的经历或背景设定，也可以简单的复制角色自身（甚至加强一部分），与其进行对战。</t>
+        <t xml:space="preserve">主動開啟：四階本能覺醒開啟之後，且度過了兩個冒險世界（包括開啟四階的那場）之後，你可以選擇挑戰心魔。當你戰勝自己的心魔之後，你可以跨入5階本能覺醒。
+每場冒險世界，你只能挑戰一次心魔。
+挑戰心魔時你進入你自身的心靈幻境中，但外界時間同步流逝，你在幻境中經過多久時間，外界也會經過同樣的時間，在戰鬥中觸發會是極端危險的狀況，此時針對外界而言，你無法控制你的角色，但是你可以依本能行動。
+這種兇險的形式對各人表現不一，通常心魔本身和度過的方法聯繫人物的扮演，個性與背景。具體的表現形式和通過判斷由ST掌握。ST可以為角色設計獨立故事，源於其故事中的經歷或背景設定，也可以簡單的複製角色自身（甚至加強一部分），與其進行對戰。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CE168">
       <text>
-        <t xml:space="preserve">自学规则：
-有些时候，规则或者资源允许你“通过自己的钻研来领悟”某些能力，即，不支付支线与奖励点数，而是通过消耗XP来学习一些能力。这被称作自学规则。
-自学规则可以购买的内容包括：
-称号主干及其技能树中的技能；
-流派主干及其技能树中的技能：
-血统技能树中的技能；
-改造技能树中的技能；
-瞳术技能树中的技能；
-魔导书的专属技能：
-修炼体系中需要花费经验的部分及其技能树的技能；
-技能自身的研发；
-已经可以学习的通用技能（如通用法术）；
-还有一些其他的能力（看对应能力的详细说明）。
-使用经验无法学些模板能力本身（无法购买高级血统，但是依旧可以购买血统技能）或物品（由于魔导书的特殊性，也无法自创）。
-对于一个自己已经拥有的技能，你可以自学其在同一技能树中的后继技能或子技能（例如在已有D级能量射击技能时修炼一个同级技巧）。</t>
+        <t xml:space="preserve">自學規則：
+有些時候，規則或者資源允許你“通過自己的鑽研來領悟”某些能力，即，不支付支線與獎勵點數，而是通過消耗XP來學習一些能力。這被稱作自學規則。
+自學規則可以購買的內容包括：
+稱號主幹及其技能樹中的技能；
+流派主幹及其技能樹中的技能：
+血統技能樹中的技能；
+改造技能樹中的技能；
+瞳術技能樹中的技能；
+魔導書的專屬技能：
+修煉體系中需要花費經驗的部分及其技能樹的技能；
+技能自身的研發；
+已經可以學習的通用技能（如通用法術）；
+還有一些其他的能力（看對應能力的詳細說明）。
+使用經驗無法學些模板能力本身（無法購買高級血統，但是依舊可以購買血統技能）或物品（由於魔導書的特殊性，也無法自創）。
+對於一個自己已經擁有的技能，你可以自學其在同一技能樹中的後繼技能或子技能（例如在已有D級能量射擊技能時修煉一個同級技巧）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CA3">
       <text>
-        <t xml:space="preserve">生理类：这类缺陷和天赋基于你的生理因素产生效果。如果你拥有夺舍或类似的可以换一具身体的能力，或者元神离体等可以不使用旧身体的能力，那么你在新的身体里不再受到生理类缺陷和生理类天赋的影响。如果你还能回到旧身体，那么你还要被旧身体中的生理类缺陷和生理类天赋影响。
-精神类：这类缺陷和天赋基于你的精神状况产生效果。如果你拥有切换人格或类似的能力，那么你在换到新人格时，旧人格的精神类缺陷和精神类天赋不能被继承，直到你换回旧人格。
-特异类：这类缺陷和天赋的生效机制根本无法被解释。可以确信的是，摆脱这类缺陷和天赋的方法是死亡，有时候也许死亡都无法解除他们。
-如果没有特殊说明，缺陷与天赋带来的都是专长加值与专长减值，并且减值都可以叠加。</t>
+        <t xml:space="preserve">生理類：這類缺陷和天賦基於你的生理因素產生效果。如果你擁有奪舍或類似的可以換一具身體的能力，或者元神離體等可以不使用舊身體的能力，那麼你在新的身體裡不再受到生理類缺陷和生理類天賦的影響。如果你還能回到舊身體，那麼你還要被舊身體中的生理類缺陷和生理類天賦影響。
+精神類：這類缺陷和天賦基於你的精神狀況產生效果。如果你擁有切換人格或類似的能力，那麼你在換到新人格時，舊人格的精神類缺陷和精神類天賦不能被繼承，直到你換回舊人格。
+特異類：這類缺陷和天賦的生效機制根本無法被解釋。可以確信的是，擺脫這類缺陷和天賦的方法是死亡，有時候也許死亡都無法解除他們。
+如果沒有特殊說明，缺陷與天賦帶來的都是專長加值與專長減值，並且減值都可以疊加。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C55">
@@ -790,44 +790,44 @@
     </comment>
     <comment authorId="0" ref="C22">
       <text>
-        <t xml:space="preserve">留意环境并查觉变化的能力，洞察力、直觉、快速分辨细节的能力。这一属性代表人物的注意力和对信息的分辨能力，因此近视眼不一定感知就低。
-任何能够感知外界的存在都拥有感知值。
-感知为0的人物失去对现实的感应，陷入无法醒来的迷梦。他将会处于“昏迷”状态。</t>
+        <t xml:space="preserve">留意環境並查覺變化的能力，洞察力、直覺、快速分辨細節的能力。這一屬性代表人物的注意力和對信息的分辨能力，因此近視眼不一定感知就低。
+任何能夠感知外界的存在都擁有感知值。
+感知為0的人物失去對現實的感應，陷入無法醒來的迷夢。他將會處於“昏迷”狀態。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI45">
       <text>
-        <t xml:space="preserve">强韧豁免：有些场合中会使用强韧豁免检定，即此项，常用于抵抗生理影响，强韧豁免检定的初始DP等于耐力+求生（自我保护）。
+        <t xml:space="preserve">強韌豁免：有些場合中會使用強韌豁免檢定，即此項，常用於抵抗生理影響，強韌豁免檢定的初始DP等於耐力+求生（自我保護）。
 </t>
       </text>
     </comment>
     <comment authorId="0" ref="BQ53">
       <text>
-        <t xml:space="preserve">效果：5阶本能觉醒获得是两个被动的强化效果：
-你获得一项价格为A+8000以下的技能，招式，技艺，从全书中选择。
-你选择的能力若需要能耗，则改为消耗等额的意志力。
-你不能选择你不满足前提的能力，如属性要求，生物类型要求等。
-你选择的能力若为法术，则现在其改为非法术能力，但是应用的检定和上限不会获得变化，并且依然保留姿势和语言，书本以及威力值，关键字等法师相关的要求，这意味着如果你不满足该要求，则无法使用。
-若该能力的前提在原本能力的主干中（比如主干说明，比如先买A再买B）则也无法获得。
-需要注意的是，本技能，招式，技艺只能在四阶本能觉醒下才能使用。
-你获得0级超凡神圣。
-神格升级：当你击杀其他五阶强者或者击败其他神明时，可以提升等级。
-你提升对应等级需要击杀或者击败目标等级对应数量等级的强者。（如从0级到1级需要击杀1个，从1级到2级需要击杀2个，从2级到3级需要击杀3个）</t>
+        <t xml:space="preserve">效果：5階本能覺醒獲得是兩個被動的強化效果：
+你獲得一項價格為A+8000以下的技能，招式，技藝，從全書中選擇。
+你選擇的能力若需要能耗，則改為消耗等額的意志力。
+你不能選擇你不滿足前提的能力，如屬性要求，生物類型要求等。
+你選擇的能力若為法術，則現在其改為非法術能力，但是應用的檢定和上限不會獲得變化，並且依然保留姿勢和語言，書本以及威力值，關鍵字等法師相關的要求，這意味著如果你不滿足該要求，則無法使用。
+若該能力的前提在原本能力的主幹中（比如主幹說明，比如先買A再買B）則也無法獲得。
+需要注意的是，本技能，招式，技藝只能在四階本能覺醒下才能使用。
+你獲得0級超凡神聖。
+神格升級：當你擊殺其他五階強者或者擊敗其他神明時，可以提升等級。
+你提升對應等級需要擊殺或者擊敗目標等級對應數量等級的強者。（如從0級到1級需要擊殺1個，從1級到2級需要擊殺2個，從2級到3級需要擊殺3個）</t>
       </text>
     </comment>
     <comment authorId="0" ref="B146">
       <text>
-        <t xml:space="preserve">手表增强组件
-每个人进入这个世界的时候，都会戴上一块由黑色的金属制成，样式古朴纯粹的手表，本手表的数据为“轮回队员手表”。一般情况下，它会显示各种数据信息，比如任务信息，新人数目等等。但你可以花费支线和分数来扩展它的能力。
-由于手表是特殊的轮回之境物品，所以其不占用任何装备位。
-手表插件没有上限。</t>
+        <t xml:space="preserve">手錶增強組件
+每個人進入這個世界的時候，都會戴上一塊由黑色的金屬製成，樣式古樸純粹的手錶，本手錶的數據為“輪迴隊員手錶”。一般情況下，它會顯示各種數據信息，比如任務信息，新人數目等等。但你可以花費支線和分數來擴展它的能力。
+由於手錶是特殊的輪迴之境物品，所以其不佔用任何裝備位。
+手錶插件沒有上限。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B113">
       <text>
-        <t xml:space="preserve">例1：你在仓库中存储了B+4000分，仓库中存有3个D+500的技能，3个C+1000的技能，3个B+2000的技能。一次短休结束后，你可以重新配置B+4000分，如获得3个C+1000的技能，剩余1000分，无法再次获得技能，也可以选择2个C+1000的技能，然后2个D+500的技能，任意组合。
-例2：你购买了2个书页，然后指定2个技能A和B，将技能A和B储存了进去，这时你还想指定技能C，但是技能C无法替换A或者B被储存进去，若要储存进去则必须再购买一页。
-例3：你在仓库中存储了BB+10000分，仓库中存有3个D+500的技能（分别称之为A、B、C），3个C+1000的技能（分别称之为D、E、F），3个B+2000的技能（分别称之为G、H、I）。你原本身上携带的是技能G和技能D、E、F，因为战斗所需，你将携带的技能配置变为了技能G、H，因为你身上携带的技能变动数达到4个（你获得1个新技能，并且将3个旧技能存放进了书签），并且这是本次冒险世界下第2次进行快速整备，因此你需要支付（4+2）/点意志力和一个完整的回合。</t>
+        <t xml:space="preserve">例1：你在倉庫中存儲了B+4000分，倉庫中存有3個D+500的技能，3個C+1000的技能，3個B+2000的技能。一次短休結束後，你可以重新配置B+4000分，如獲得3個C+1000的技能，剩餘1000分，無法再次獲得技能，也可以選擇2個C+1000的技能，然後2個D+500的技能，任意組合。
+例2：你購買了2個書頁，然後指定2個技能A和B，將技能A和B儲存了進去，這時你還想指定技能C，但是技能C無法替換A或者B被儲存進去，若要儲存進去則必須再購買一頁。
+例3：你在倉庫中存儲了BB+10000分，倉庫中存有3個D+500的技能（分別稱之為A、B、C），3個C+1000的技能（分別稱之為D、E、F），3個B+2000的技能（分別稱之為G、H、I）。你原本身上攜帶的是技能G和技能D、E、F，因為戰鬥所需，你將攜帶的技能配置變為了技能G、H，因為你身上攜帶的技能變動數達到4個（你獲得1個新技能，並且將3箇舊技能存放進了書籤），並且這是本次冒險世界下第2次進行快速整備，因此你需要支付（4+2）/點意志力和一個完整的回合。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C47">
@@ -843,66 +843,66 @@
     </comment>
     <comment authorId="0" ref="CP168">
       <text>
-        <t xml:space="preserve">普通专长：这些专长代表的是普通人即可学习，相对比较简单。
-要学习一个普通专长，必须为普通专长所需的每个专长等级投入3点XP，若一个普通专长拥有多个等级，你必须为每一等级单独学习，并且必须按顺序学习。
-因此，一个具有1-5级的专长，一共需要3+6+9+12+15=45XP来完全掌握。
-若一个专长直接以高等级开始，则可以直接花费对应等级的XP即可获得。
-因此，一个具有2-3级的专长，一共需要6+9=15XP来掌握。
-轮回之境专长：该专长包括非凡的才能，比如超魔专长等等，一般情况下，其前提条件都包括一些非凡的要求。
-要学习一个轮回之境专长，必须为轮回之境专长所需的每个专长等级投入6点XP，若一个普通专长拥有多个等级，你必须为每一等级单独学习，并且必须按顺序学习。
-因此，一个具有1-5级的专长，一共需要6+12+18+24+30=90XP来完全掌握。
-若一个专长直接以高等级开始，则可以直接花费对应等级的XP即可获得。
-因此，一个具有2-3级的专长，一共需要12+18=30XP来掌握。</t>
+        <t xml:space="preserve">普通專長：這些專長代表的是普通人即可學習，相對比較簡單。
+要學習一個普通專長，必須為普通專長所需的每個專長等級投入3點XP，若一個普通專長擁有多個等級，你必須為每一等級單獨學習，並且必須按順序學習。
+因此，一個具有1-5級的專長，一共需要3+6+9+12+15=45XP來完全掌握。
+若一個專長直接以高等級開始，則可以直接花費對應等級的XP即可獲得。
+因此，一個具有2-3級的專長，一共需要6+9=15XP來掌握。
+輪迴之境專長：該專長包括非凡的才能，比如超魔專長等等，一般情況下，其前提條件都包括一些非凡的要求。
+要學習一個輪迴之境專長，必須為輪迴之境專長所需的每個專長等級投入6點XP，若一個普通專長擁有多個等級，你必須為每一等級單獨學習，並且必須按順序學習。
+因此，一個具有1-5級的專長，一共需要6+12+18+24+30=90XP來完全掌握。
+若一個專長直接以高等級開始，則可以直接花費對應等級的XP即可獲得。
+因此，一個具有2-3級的專長，一共需要12+18=30XP來掌握。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AB5">
       <text>
-        <t xml:space="preserve">自然恢复：
-角色们就算超凡入圣，也是需要一定休息的。
-角色需要花时间吃东西，睡觉，护理伤势，回复能量，为未来的战斗做准备。
-角色以及任何生物可以在24小时之内任何时间进行短休，并且不算次数。
-角色以及任何生物只能在24小时内进行一次长休。
+        <t xml:space="preserve">自然恢復：
+角色們就算超凡入聖，也是需要一定休息的。
+角色需要花時間吃東西，睡覺，護理傷勢，回覆能量，為未來的戰鬥做準備。
+角色以及任何生物可以在24小時之內任何時間進行短休，並且不算次數。
+角色以及任何生物只能在24小時內進行一次長休。
 短休：
-短休是一段短暂的休整时刻。需要至少1个小时的时间，角色们在这期间进行饮食，吃饭，休息，打坐，冥想，聊天等活动。
-如果休息过程中被打扰（如进入战斗，高强度的移动等）则休息被打断，角色必须重新开始休息才能获得短休的效果。
-每进行一次至少1小时的短休息（不能做其他行动），可以将全部状态为B的生命值恢复为完好。
-每进行一次至少1小时的短休息（不能做其他行动），可以选择自己拥有的一种不良状态点数，获得一次豁免的机会。
-每进行一次至少1小时的短休息（不能做其他行动），恢复1点意志力。
-若你拥有一个自然恢复速度翻倍的能力，则休息时间减短为半小时。
-若你拥有多个自然恢复速度翻倍的能力，则休息时间改为15分钟。
-长休：
-长休是一段更为舒适的休整时刻。需要至少 8 个小时的时间，角色在这期间进行睡眠，饮食，聊天，打坐，冥想，放哨，修整，聊天等。
-如果休息过程中被打扰（如进入战斗，高强度的移动等）则休息被打断，角色必须重新开始休息才能获得长休的效果。
-每进行一次至少8小时的长休息（不能做其他行动，而是用于睡眠之类）），可以将全部状态为L的生命值恢复为完好，或者将全部状态为A的生命值转化为L。
-每进行至少8小时的长休息（不进行任何行动，而是用于睡眠之类），人物可以投掷1D10，这不是一次检定，恢复该投骰结果+传奇决心+传奇沉着/点意志力。
-每连续进行至少8小时的长休息（不进行任何行动，而是用于睡眠之类），可以恢复1点属性伤害。
-每连续进行至少8小时的长休息（不进行任何行动，而是用于睡眠之类），可以针对自己拥有的所有不良状态点数，获得一次豁免的机会。
-若你拥有一个自然恢复速度翻倍的能力，则休息时间简短为4小时。
-若你拥有多个自然恢复速度翻倍的能力，则休息时间改为2小时。
-一些药物，医疗或者超自然能力可以加快回复的速度，或立即恢复一些生命值。
-这些效果与短休或者长休的效果叠加。</t>
+短休是一段短暫的休整時刻。需要至少1個小時的時間，角色們在這期間進行飲食，吃飯，休息，打坐，冥想，聊天等活動。
+如果休息過程中被打擾（如進入戰鬥，高強度的移動等）則休息被打斷，角色必須重新開始休息才能獲得短休的效果。
+每進行一次至少1小時的短休息（不能做其他行動），可以將全部狀態為B的生命值恢復為完好。
+每進行一次至少1小時的短休息（不能做其他行動），可以選擇自己擁有的一種不良狀態點數，獲得一次豁免的機會。
+每進行一次至少1小時的短休息（不能做其他行動），恢復1點意志力。
+若你擁有一個自然恢復速度翻倍的能力，則休息時間減短為半小時。
+若你擁有多個自然恢復速度翻倍的能力，則休息時間改為15分鐘。
+長休：
+長休是一段更為舒適的休整時刻。需要至少 8 個小時的時間，角色在這期間進行睡眠，飲食，聊天，打坐，冥想，放哨，修整，聊天等。
+如果休息過程中被打擾（如進入戰鬥，高強度的移動等）則休息被打斷，角色必須重新開始休息才能獲得長休的效果。
+每進行一次至少8小時的長休息（不能做其他行動，而是用於睡眠之類）），可以將全部狀態為L的生命值恢復為完好，或者將全部狀態為A的生命值轉化為L。
+每進行至少8小時的長休息（不進行任何行動，而是用於睡眠之類），人物可以投擲1D10，這不是一次檢定，恢復該投骰結果+傳奇決心+傳奇沉著/點意志力。
+每連續進行至少8小時的長休息（不進行任何行動，而是用於睡眠之類），可以恢復1點屬性傷害。
+每連續進行至少8小時的長休息（不進行任何行動，而是用於睡眠之類），可以針對自己擁有的所有不良狀態點數，獲得一次豁免的機會。
+若你擁有一個自然恢復速度翻倍的能力，則休息時間簡短為4小時。
+若你擁有多個自然恢復速度翻倍的能力，則休息時間改為2小時。
+一些藥物，醫療或者超自然能力可以加快回復的速度，或立即恢復一些生命值。
+這些效果與短休或者長休的效果疊加。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BX53">
       <text>
-        <t xml:space="preserve">本级别效果为被动，所以没有持续时间。</t>
+        <t xml:space="preserve">本級別效果為被動，所以沒有持續時間。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI37">
       <text>
-        <t xml:space="preserve">生命值：生命值代表角色的生命力，角色受伤会使自身的生命值向不良的情况转化，具体的内容请看“生命章节”，生命值的大小为耐力+体型带来的生命值调整。</t>
+        <t xml:space="preserve">生命值：生命值代表角色的生命力，角色受傷會使自身的生命值向不良的情況轉化，具體的內容請看“生命章節”，生命值的大小為耐力+體型帶來的生命值調整。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CO69">
       <text>
-        <t xml:space="preserve">掩蔽防御：
-掩蔽加值可能会加在防御和对抗范围效果的检定上，当然其必须单独说明是加在防御还是对抗范围效果上，若没有特殊说明，则一般是指防御，它意味着某些物品挡在你与危险之间。
-掩蔽防御不会叠加。</t>
+        <t xml:space="preserve">掩蔽防禦：
+掩蔽加值可能會加在防禦和對抗範圍效果的檢定上，當然其必須單獨說明是加在防禦還是對抗範圍效果上，若沒有特殊說明，則一般是指防禦，它意味著某些物品擋在你與危險之間。
+掩蔽防禦不會疊加。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B138">
       <text>
-        <t xml:space="preserve">腰带：戴在腰间的装备，每个角色只有一个腰带位。</t>
+        <t xml:space="preserve">腰帶：戴在腰間的裝備，每個角色只有一個腰帶位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AX153">
@@ -924,79 +924,79 @@
     <comment authorId="0" ref="AJ5">
       <text>
         <t xml:space="preserve">能量池
-能量是一种运用和获得力量的方式。如果没有特殊描述，能量池不具备排它性。
-每种能量在获得时，都会同时获得它的运作机制（包括使用何者作为关键属性，如何恢复、补充、有否有基本用法等等）。
-如果没有特殊说明，其他能力不会干涉这种运作机制，而是作为这种运作机制的补充。
-如：短休可以恢复魔力，若你拥有自然恢复减半的能力，则你恢复魔力的时间也会减半。
-所有的能量都是超自然能力，除非有特殊说明。</t>
+能量是一種運用和獲得力量的方式。如果沒有特殊描述，能量池不具備排它性。
+每種能量在獲得時，都會同時獲得它的運作機制（包括使用何者作為關鍵屬性，如何恢復、補充、有否有基本用法等等）。
+如果沒有特殊說明，其他能力不會干涉這種運作機制，而是作為這種運作機制的補充。
+如：短休可以恢復魔力，若你擁有自然恢復減半的能力，則你恢復魔力的時間也會減半。
+所有的能量都是超自然能力，除非有特殊說明。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B130">
       <text>
-        <t xml:space="preserve">人物装备位
-轮回之境提供了便利和强大的道具，使人坚不可摧、日行千里、腾云驾雾。但是，没有人可以把所有好东西都用在自己身上。一个人身上所能使用的物品是有限的，有时是基于常理，有时是基于物品本身的特性。
-对于有些物品而言，其必须以一定的方法安置在身上的某些位置才能生效。而装备位表明了该类物品彼此之间互相排斥、无法共同生效的本质特性。
-一个装备位与一个人体的生理位置相关，但并不是特指这个位置，而是指该生理位置对于那些必须装备于此位置的物品的限制。
-受到某个装备位限制的一类物品只有特定的一个（戒指位是两个）生效，有时是因为物品自然的超自然能量场需要在特定的生理位置与人体能量场产生互相作用，有时是因为该生理位置在魔法或宗教表征上具有特殊的意义。无论如何，如果某件物品需要装备在某个装备位所关联的生理位置上，但该物品本身并不占用装备位，则此装备位依然视为未被占用。
-同装备位装备多件物品：有时一个装备位上会佩带多件物品，比如在手上戴多个戒指，或在头上同时佩戴魔法头巾、帽子、头盔等。在这种情况下，只有一件物品（或符合装备位要求的数量）会生效，由角色来决定。
-请注意，上述的装备位必须代表着角色有对应的生理位，若角色的生理位发生了改变，则对应的装备位也会发生改变。
-例：若角色没有腿则失去“鞋”这个装备位。
-例：若角色失去一只手，则失去手套位，护腕位（这些必须成对才能生效）以及一个戒指位。
-例：角色拥有4只手，额外可以持有多把武器。
-例：角色拥有2个头，额外获得1个头盔位和项链位。</t>
+        <t xml:space="preserve">人物裝備位
+輪迴之境提供了便利和強大的道具，使人堅不可摧、日行千里、騰雲駕霧。但是，沒有人可以把所有好東西都用在自己身上。一個人身上所能使用的物品是有限的，有時是基於常理，有時是基於物品本身的特性。
+對於有些物品而言，其必須以一定的方法安置在身上的某些位置才能生效。而裝備位表明了該類物品彼此之間互相排斥、無法共同生效的本質特性。
+一個裝備位與一個人體的生理位置相關，但並不是特指這個位置，而是指該生理位置對於那些必須裝備於此位置的物品的限制。
+受到某個裝備位限制的一類物品只有特定的一個（戒指位是兩個）生效，有時是因為物品自然的超自然能量場需要在特定的生理位置與人體能量場產生互相作用，有時是因為該生理位置在魔法或宗教表徵上具有特殊的意義。無論如何，如果某件物品需要裝備在某個裝備位所關聯的生理位置上，但該物品本身並不佔用裝備位，則此裝備位依然視為未被佔用。
+同裝備位裝備多件物品：有時一個裝備位上會佩帶多件物品，比如在手上戴多個戒指，或在頭上同時佩戴魔法頭巾、帽子、頭盔等。在這種情況下，只有一件物品（或符合裝備位要求的數量）會生效，由角色來決定。
+請注意，上述的裝備位必須代表著角色有對應的生理位，若角色的生理位發生了改變，則對應的裝備位也會發生改變。
+例：若角色沒有腿則失去“鞋”這個裝備位。
+例：若角色失去一隻手，則失去手套位，護腕位（這些必須成對才能生效）以及一個戒指位。
+例：角色擁有4隻手，額外可以持有多把武器。
+例：角色擁有2個頭，額外獲得1個頭盔位和項鍊位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="X22">
       <text>
-        <t xml:space="preserve">在感知相关的检定上获得n个附加成功。
-获得n点防御附加成功。
-获得n点基础防御。
-基础敏感范围增加20n米。</t>
+        <t xml:space="preserve">在感知相關的檢定上獲得n個附加成功。
+獲得n點防禦附加成功。
+獲得n點基礎防禦。
+基礎敏感範圍增加20n米。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CW3">
       <text>
-        <t xml:space="preserve">生理类：这类缺陷和天赋基于你的生理因素产生效果。如果你拥有夺舍或类似的可以换一具身体的能力，或者元神离体等可以不使用旧身体的能力，那么你在新的身体里不再受到生理类缺陷和生理类天赋的影响。如果你还能回到旧身体，那么你还要被旧身体中的生理类缺陷和生理类天赋影响。
-精神类：这类缺陷和天赋基于你的精神状况产生效果。如果你拥有切换人格或类似的能力，那么你在换到新人格时，旧人格的精神类缺陷和精神类天赋不能被继承，直到你换回旧人格。
-特异类：这类缺陷和天赋的生效机制根本无法被解释。可以确信的是，摆脱这类缺陷和天赋的方法是死亡，有时候也许死亡都无法解除他们。
-如果没有特殊说明，缺陷与天赋带来的都是专长加值与专长减值。</t>
+        <t xml:space="preserve">生理類：這類缺陷和天賦基於你的生理因素產生效果。如果你擁有奪舍或類似的可以換一具身體的能力，或者元神離體等可以不使用舊身體的能力，那麼你在新的身體裡不再受到生理類缺陷和生理類天賦的影響。如果你還能回到舊身體，那麼你還要被舊身體中的生理類缺陷和生理類天賦影響。
+精神類：這類缺陷和天賦基於你的精神狀況產生效果。如果你擁有切換人格或類似的能力，那麼你在換到新人格時，舊人格的精神類缺陷和精神類天賦不能被繼承，直到你換回舊人格。
+特異類：這類缺陷和天賦的生效機制根本無法被解釋。可以確信的是，擺脫這類缺陷和天賦的方法是死亡，有時候也許死亡都無法解除他們。
+如果沒有特殊說明，缺陷與天賦帶來的都是專長加值與專長減值。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CE177">
       <text>
-        <t xml:space="preserve">自制物品和修复物品的步骤：
-1.得到图纸。
-通过兑换，这种方式只能兑换轮回之境所允许兑换的物品的对应图纸。价格为改物品的【支线等级×分数/100】点奖励点数，向上取整。（双支线物品为对应单支线+0.5）
-2.解读图纸。
-解读科学图纸，研究文件的信息。
-检定：智力+科学（对应专业）
-动作：这是一个周期性检定，周期为一小时，这意味着只要你潜心研究，则一定可以获得成功。
-解读图纸的DC等于【物品的图纸价格】或【物品的支线等级×5（向上取整）】取较高者。
-一个物品的图纸解读只需要进行一次。
-3. 准备机床。
-任何维修以及制造皆需要对应的辅助设备（工具），原支线等级D级以上的物品，在制造时需要额外的加工组合设备，这些加工设备视为功能齐全的辅助装置，比如纳米机器人群或高性能数控机床等等，可以适用于所有同级物品的制造，并且同样属于科技本质，并且高等级的辅助装置可以向下兼容低等级的辅助装置。
-制造和维修无支线物品的辅助设备在轮回之境中视为免费，无需工具。
-制造和维修D级物品的辅助设备兑换价格为D+1000点
-制造和维修C级物品的辅助设备兑换价格为C+2000点
-制造和维修B级物品的辅助设备兑换价格为B+4000点
-制造和维修A级物品的辅助设备兑换价格为A+8000点
-但是魔幻本质和科技本质所需要的是两套设备，也就是说，如果你想制作科技本质的物品则需要一套，再想制造魔幻本质需要再来一套魔幻本质的，双方无法混用。
-4. 购买零件和材料。
-如果在轮回之境兑换零件进行制造，则价格为原本的1/3，支线要求降低一个等级（如果是D级支线的物品，拆成实际上并不存在的E级支线处理，E级支线只能用于兑换D级物品的材料）
-如果用轮回之境兑换零件进行维修，则无需支线，将其分数/载具结构值，结果向上取整。每修复1点结构值则损耗对应的分数。
-5.制造与修复
-制造：
-你现在可以制作对应的物品了。
-检定：智力+手艺-对应手艺子技能
-动作：这是一个周期性检定，周期为一天，DC为支线等级×分数/100，向上取整。
-这意味着只要你潜心制作，则一定可以获得成功。
-特殊：对于无支线且DC不到1的物品可以在一天中制造多件,需要的总分数相加，直到DC达到1。
-修复：
-你现在可以维修对应的物品了。
-检定：智力+手艺-对应手艺子技能
-动作：这是一个周期性检定，周期为一小时，每当成功数到达其硬度，则恢复1点结构值。
-这意味着只要你潜心修理，则一定可以获得成功。
-需要注意的是，针对你所要修复的物品，你必须已经解读其图纸，并且相关属性和技能满足制造该物品的条件。</t>
+        <t xml:space="preserve">自制物品和修復物品的步驟：
+1.得到圖紙。
+通過兌換，這種方式只能兌換輪迴之境所允許兌換的物品的對應圖紙。價格為改物品的【支線等級×分數/100】點獎勵點數，向上取整。（雙支線物品為對應單支線+0.5）
+2.解讀圖紙。
+解讀科學圖紙，研究文件的信息。
+檢定：智力+科學（對應專業）
+動作：這是一個週期性檢定，週期為一小時，這意味著只要你潛心研究，則一定可以獲得成功。
+解讀圖紙的DC等於【物品的圖紙價格】或【物品的支線等級×5（向上取整）】取較高者。
+一個物品的圖紙解讀只需要進行一次。
+3. 準備機床。
+任何維修以及製造皆需要對應的輔助設備（工具），原支線等級D級以上的物品，在製造時需要額外的加工組合設備，這些加工設備視為功能齊全的輔助裝置，比如納米機器人群或高性能數控機床等等，可以適用於所有同級物品的製造，並且同樣屬於科技本質，並且高等級的輔助裝置可以向下兼容低等級的輔助裝置。
+製造和維修無支線物品的輔助設備在輪迴之境中視為免費，無需工具。
+製造和維修D級物品的輔助設備兌換價格為D+1000點
+製造和維修C級物品的輔助設備兌換價格為C+2000點
+製造和維修B級物品的輔助設備兌換價格為B+4000點
+製造和維修A級物品的輔助設備兌換價格為A+8000點
+但是魔幻本質和科技本質所需要的是兩套設備，也就是說，如果你想製作科技本質的物品則需要一套，再想製造魔幻本質需要再來一套魔幻本質的，雙方無法混用。
+4. 購買零件和材料。
+如果在輪迴之境兌換零件進行製造，則價格為原本的1/3，支線要求降低一個等級（如果是D級支線的物品，拆成實際上並不存在的E級支線處理，E級支線只能用於兌換D級物品的材料）
+如果用輪迴之境兌換零件進行維修，則無需支線，將其分數/載具結構值，結果向上取整。每修復1點結構值則損耗對應的分數。
+5.製造與修復
+製造：
+你現在可以製作對應的物品了。
+檢定：智力+手藝-對應手藝子技能
+動作：這是一個週期性檢定，週期為一天，DC為支線等級×分數/100，向上取整。
+這意味著只要你潛心製作，則一定可以獲得成功。
+特殊：對於無支線且DC不到1的物品可以在一天中製造多件,需要的總分數相加，直到DC達到1。
+修復：
+你現在可以維修對應的物品了。
+檢定：智力+手藝-對應手藝子技能
+動作：這是一個週期性檢定，週期為一小時，每當成功數到達其硬度，則恢復1點結構值。
+這意味著只要你潛心修理，則一定可以獲得成功。
+需要注意的是，針對你所要修復的物品，你必須已經解讀其圖紙，並且相關屬性和技能滿足製造該物品的條件。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C31">
@@ -1017,46 +1017,46 @@
     </comment>
     <comment authorId="0" ref="Q138">
       <text>
-        <t xml:space="preserve">鞋：穿在脚上的装备，每个角色只有一个鞋位。</t>
+        <t xml:space="preserve">鞋：穿在腳上的裝備，每個角色只有一個鞋位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C23">
       <text>
-        <t xml:space="preserve">人物果敢的决断力和决定的坚定程度，也代表了人物顽固的程度。在超自然意义上，代表了人物的精神的强度。
-任何能够有目的行动的存在都拥有决心值。
-决心为0的人物失去行为能力。他将会处于“昏迷”状态。</t>
+        <t xml:space="preserve">人物果敢的決斷力和決定的堅定程度，也代表了人物頑固的程度。在超自然意義上，代表了人物的精神的強度。
+任何能夠有目的行動的存在都擁有決心值。
+決心為0的人物失去行為能力。他將會處於“昏迷”狀態。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AZ5">
       <text>
-        <t xml:space="preserve">不良状态：
-是指人物正处于某种负面的效果之中，这些效果一般会在一定的情况下带来减值，这称为不良状态。
-不良状态是一种状态：当人物处于该状态下，会获得某些特定的固有效果。
-有些固有不良状态无需计算，获得之后，人物会立即受到该固定效果的影响。诸如：定身，震慑，浮空等。
-不良状态点数：
-角色还有一些不良状态则根据不良状态点数进行计算，此时角色会根据其身上的不良状态点数从而获得某些效果的影响。
-轻度：只要拥有不良状态点数即可
-重度：点数&gt;【关键抵抗属性较高者*（关键抵抗属性较高者上的传奇属性+1）】
-进入重度不良状态之后，如无特殊说明，则人物依然要受到轻度不良状态所描述的减值。
-毁灭：点数&gt;【关键抵抗属性之和*（关键抵抗属性上的传奇属性之和+1）】 
-进入毁灭性后果之后，如无特殊说明，则人物依旧要受到轻度不良状态所描述的减值，并且承受重度不良状态。
-注意：当不良状态点数恢复到关键抵抗属性之下时，重度不良状态恢复为轻度不良状态；但是毁灭性后果不会因为不良状态点数恢复而自动移除，只会被轮回之境或者一些存在特殊说明可以解除毁灭性后果的能力所解除。
+        <t xml:space="preserve">不良狀態：
+是指人物正處於某種負面的效果之中，這些效果一般會在一定的情況下帶來減值，這稱為不良狀態。
+不良狀態是一種狀態：當人物處於該狀態下，會獲得某些特定的固有效果。
+有些固有不良狀態無需計算，獲得之後，人物會立即受到該固定效果的影響。諸如：定身，震懾，浮空等。
+不良狀態點數：
+角色還有一些不良狀態則根據不良狀態點數進行計算，此時角色會根據其身上的不良狀態點數從而獲得某些效果的影響。
+輕度：只要擁有不良狀態點數即可
+重度：點數&gt;【關鍵抵抗屬性較高者*（關鍵抵抗屬性較高者上的傳奇屬性+1）】
+進入重度不良狀態之後，如無特殊說明，則人物依然要受到輕度不良狀態所描述的減值。
+毀滅：點數&gt;【關鍵抵抗屬性之和*（關鍵抵抗屬性上的傳奇屬性之和+1）】 
+進入毀滅性後果之後，如無特殊說明，則人物依舊要受到輕度不良狀態所描述的減值，並且承受重度不良狀態。
+注意：當不良狀態點數恢復到關鍵抵抗屬性之下時，重度不良狀態恢復為輕度不良狀態；但是毀滅性後果不會因為不良狀態點數恢復而自動移除，只會被輪迴之境或者一些存在特殊說明可以解除毀滅性後果的能力所解除。
 </t>
       </text>
     </comment>
     <comment authorId="0" ref="BI46">
       <text>
-        <t xml:space="preserve">心灵检定（心灵能力）
-需要使用心灵检定的情况千奇百怪，根据对应的能力决定。
-心灵检定一般是使用者依靠自身强大的精神力或者心灵的力量施展出来的能力，若该能力需要检定，则心灵检定为决心+沉着±相关调整值。
-若该能力对一个目标进行攻击，则根据攻击的方式和所使用的武器，其心灵检定为决心+沉着-目标防御±相关调整值。
-心灵检定的上限为=决心值+沉着值。这代表着即使你最终投出来的成功数超过了这个心灵检定上限，也只能造成相当于上限的成功数。
-若是使用心灵检定进行攻击，则伤害上限=决心值+沉着值，这代表着即使你最终造成的伤害超过了这个心灵检定上限，也只能造成相当于上限的伤害。</t>
+        <t xml:space="preserve">心靈檢定（心靈能力）
+需要使用心靈檢定的情況千奇百怪，根據對應的能力決定。
+心靈檢定一般是使用者依靠自身強大的精神力或者心靈的力量施展出來的能力，若該能力需要檢定，則心靈檢定為決心+沉著±相關調整值。
+若該能力對一個目標進行攻擊，則根據攻擊的方式和所使用的武器，其心靈檢定為決心+沉著-目標防禦±相關調整值。
+心靈檢定的上限為=決心值+沉著值。這代表著即使你最終投出來的成功數超過了這個心靈檢定上限，也只能造成相當於上限的成功數。
+若是使用心靈檢定進行攻擊，則傷害上限=決心值+沉著值，這代表著即使你最終造成的傷害超過了這個心靈檢定上限，也只能造成相當於上限的傷害。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B48">
       <text>
-        <t xml:space="preserve">互动系技能：互动系技能往往是技巧与知识的结合，与生理系技能相似，如果互动系技能为0，你仍然可以尝试进行检定，但是会失去两个自然成功数，其中有一部分技能，甚至是一部分技能的一部分用法，ST可以认定为0时无法检定，视为结果自动失败，例如表达-弹奏钢琴。</t>
+        <t xml:space="preserve">互動系技能：互動系技能往往是技巧與知識的結合，與生理系技能相似，如果互動系技能為0，你仍然可以嘗試進行檢定，但是會失去兩個自然成功數，其中有一部分技能，甚至是一部分技能的一部分用法，ST可以認定為0時無法檢定，視為結果自動失敗，例如表達-彈奏鋼琴。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C48">
@@ -1072,17 +1072,17 @@
     </comment>
     <comment authorId="0" ref="BI38">
       <text>
-        <t xml:space="preserve">触及范围：触及范围一般决定战斗中你的威胁范围，默认的威胁范围为你的体积带来的触及范围，触及范围决定的是角色近战攻击的范围。
-有一些特殊能力或者体积较大的武器会带来额外的触及范围，一般是每有6点体积的武器则可以额外带来2米的触及范围（延伸1格）。</t>
+        <t xml:space="preserve">觸及範圍：觸及範圍一般決定戰鬥中你的威脅範圍，默認的威脅範圍為你的體積帶來的觸及範圍，觸及範圍決定的是角色近戰攻擊的範圍。
+有一些特殊能力或者體積較大的武器會帶來額外的觸及範圍，一般是每有6點體積的武器則可以額外帶來2米的觸及範圍（延伸1格）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CE153">
       <text>
-        <t xml:space="preserve">属性：
-分数购买：属性提升1点的价格为当前基础属性值*200分，因此将力量从1提升到5需要200+400+600+800=2000分，这种情况下提升的属性称之为基础属性。
-经验购买：属性提升1点的价格为当前基础属性值*4XP，因此将力量从1提升到5需要4+8+12+16=40XP，这种情况下提升的属性称之为基础属性。
-在使用分数和经验兑换属性时，不计算购买的能力、受到的属性伤害，只计算基础属性进行购买。
-特殊的，当你将一个基础属性从0买至1时，若使用分数，则只需花费100分，若使用经验值，则只需花费1XP。</t>
+        <t xml:space="preserve">屬性：
+分數購買：屬性提升1點的價格為當前基礎屬性值*200分，因此將力量從1提升到5需要200+400+600+800=2000分，這種情況下提升的屬性稱之為基礎屬性。
+經驗購買：屬性提升1點的價格為當前基礎屬性值*4XP，因此將力量從1提升到5需要4+8+12+16=40XP，這種情況下提升的屬性稱之為基礎屬性。
+在使用分數和經驗兌換屬性時，不計算購買的能力、受到的屬性傷害，只計算基礎屬性進行購買。
+特殊的，當你將一個基礎屬性從0買至1時，若使用分數，則只需花費100分，若使用經驗值，則只需花費1XP。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C40">
@@ -1098,9 +1098,9 @@
     </comment>
     <comment authorId="0" ref="X23">
       <text>
-        <t xml:space="preserve">在决心相关的检定上获得n个附加成功。
+        <t xml:space="preserve">在決心相關的檢定上獲得n個附加成功。
 意志力池提升3n。
-意志豁免检定获得n*3DP完美加值。</t>
+意志豁免檢定獲得n*3DP完美加值。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C32">
@@ -1117,85 +1117,85 @@
     <comment authorId="0" ref="CP153">
       <text>
         <t xml:space="preserve">技能：
-提升技能需要（当前技能等级）*2XP。
-特殊的，将技能从0级提升到1级需要1XP。
-技能最多被提升到15级。
-经验减免：
-随着技能等级的提升，玩家可以无师自通的习得某些能力和技巧。这表现为当玩家的技能等级在达到6、8、10、12、14时分别可以选择一个前提条件包括原本该技能的专长或原本基于该技能使用的自创技能，在学习该专长或自创该技能时减少6/12/24/48/96点经验值的消耗，最低将消耗降低为0。
-减少的经验不能分摊到多个不同的能力上（同一专长/称号中的不同等级认为是不同能力），但是减少的经验可以叠加到一个能力上，并非在选择该专长或能力时就要同时学习，因此若一个能力需要70XP，角色可以在技能等级到12时，累积为该技能减少90XP消耗，这样做可以免费获得这个能力。
-只用通过XP或者永久提升的方式获得的技能等级，才可以享受XP减免，任何复制，临时提升，直接变为某一等级等方式无法获得经验减免。
-经验减免针对同一个角色只能奏效一次，若出现继承情况，则计算其继承前的情况，若使用过减免，则继承后该减免机会依然算做被用掉。若出现合体情况，则计算其合体前的情况，只有永久合体才能够使用经验减免，此时合体后根据继承原本角色的技能等级决定是否可以使用经验减免，若原本该角色使用过，则算作被用过，否则可以使用。如果出现其他情况，则根据上述情况由ST判断。
-特殊的，若一个技能有无数子技能，例如表达，手艺等，无论有多少子技能满足获得经验减免条件，经验减免也只能获得一次。
-某些能力将自动提升技能等级，当你失去这些能力时（如洗点），则计算你在本技能上投入的有效经验，然后重新购买一次，多余的经验也必须投入到本技能中，直至补全剩余经验如常升级。（如技能等级2，自动提升到3，然后玩家花费6XP提升到4级，这个时候进行了洗点，则技能变回2，然后本技能投入了4点经验，技能等级变为3，然后本技能中计入2点经验，直至再投入2点经验，则升级到4级）。</t>
+提升技能需要（當前技能等級）*2XP。
+特殊的，將技能從0級提升到1級需要1XP。
+技能最多被提升到15級。
+經驗減免：
+隨著技能等級的提升，玩家可以無師自通的習得某些能力和技巧。這表現為當玩家的技能等級在達到6、8、10、12、14時分別可以選擇一個前提條件包括原本該技能的專長或原本基於該技能使用的自創技能，在學習該專長或自創該技能時減少6/12/24/48/96點經驗值的消耗，最低將消耗降低為0。
+減少的經驗不能分攤到多個不同的能力上（同一專長/稱號中的不同等級認為是不同能力），但是減少的經驗可以疊加到一個能力上，並非在選擇該專長或能力時就要同時學習，因此若一個能力需要70XP，角色可以在技能等級到12時，累積為該技能減少90XP消耗，這樣做可以免費獲得這個能力。
+只用通過XP或者永久提升的方式獲得的技能等級，才可以享受XP減免，任何複製，臨時提升，直接變為某一等級等方式無法獲得經驗減免。
+經驗減免針對同一個角色只能奏效一次，若出現繼承情況，則計算其繼承前的情況，若使用過減免，則繼承後該減免機會依然算做被用掉。若出現合體情況，則計算其合體前的情況，只有永久合體才能夠使用經驗減免，此時合體後根據繼承原本角色的技能等級決定是否可以使用經驗減免，若原本該角色使用過，則算作被用過，否則可以使用。如果出現其他情況，則根據上述情況由ST判斷。
+特殊的，若一個技能有無數子技能，例如表達，手藝等，無論有多少子技能滿足獲得經驗減免條件，經驗減免也只能獲得一次。
+某些能力將自動提升技能等級，當你失去這些能力時（如洗點），則計算你在本技能上投入的有效經驗，然後重新購買一次，多餘的經驗也必須投入到本技能中，直至補全剩餘經驗如常升級。（如技能等級2，自動提升到3，然後玩家花費6XP提升到4級，這個時候進行了洗點，則技能變回2，然後本技能投入了4點經驗，技能等級變為3，然後本技能中計入2點經驗，直至再投入2點經驗，則升級到4級）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C24">
       <text>
-        <t xml:space="preserve">人物的气质、风度和存在感，不由地引起旁人兴趣的能力。在超自然意义上，也代表了人物在多大程度上超脱了自然本质。虽然与相貌有关，但数值高并不意味着长得帅或美丽，数值低也不一定是丑八怪。
-任何能够将自己与环境区分开的存在都拥有风度值。
-风度为0的人物失去意识。他将会处于“昏迷”状态。</t>
+        <t xml:space="preserve">人物的氣質、風度和存在感，不由地引起旁人興趣的能力。在超自然意義上，也代表了人物在多大程度上超脫了自然本質。雖然與相貌有關，但數值高並不意味著長得帥或美麗，數值低也不一定是醜八怪。
+任何能夠將自己與環境區分開的存在都擁有風度值。
+風度為0的人物失去意識。他將會處於“昏迷”狀態。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI47">
       <text>
-        <t xml:space="preserve">注：开启本能觉醒检定虽然名为检定，但是不受到任何增加检定结果，或者检定DP能力的影响，除非特别说明。
-注：开启本能觉醒只有在未开启对应阶段的本能觉醒状态下才可以开启，无论是出于主动还是被动的情况下。
-注：【当你已经可以开启相应阶段的本能觉醒时】，若再次达成开启本能觉醒的条件，则【自动开启】对应阶段的本能觉醒。（如你拥有2阶的本能觉醒，之后你因一次伤害受到了恶性伤害，则你立即自动开启2阶本能觉醒）
-开启本能觉醒的条件包括：
-1）自身受到实际伤害，且结算该实际伤害后，导致自身的生命槽已经全部填满，且最严重的是恶性时。
-2）自身受到足以致死的伤害或效果时。
-3）自身珍重的人或者队友，造人受到致死伤害时。（ST应当根据RP来决定人，队友或造人是否被珍视）
-4）自身因任意不良状态点数，进入该点数对应的严重后果时。
-5）自身因任意不良状态点数，进入该点数对应的毁灭后果时。
-6）自身全神灌注做一件非常紧急且重要的事情时。（此条ST选开）
-补充1：无论如何，受到冲击伤害无法开启本能觉醒。
-补充2：当玩家处于生命值上限减少的状态时，计算条件按照当前的生命值上限来计算。
-补充3：任何自自残技能或者招式等类似能力无法让你开启本能觉醒，哪怕会让你死亡。
-补充4：无论任何条件，队友以及友军等类似的误伤或者有意的行为，不得让你开启本能觉醒。
-补充5：每条每场景只会触发一次，反复治疗或者降低不良状态点数不会额外获得开启机会，但4,5条针对每种负面状态一次。
-补充5：若一次效果会触发多条，那么你有多个开启机会（例如你受到一个效果同时将你两个负面状态从轻度直接打进毁灭，你就有4次开启机会。）
-补充6：队友的致死伤害只需其在你敏感视觉范围内，规则上死亡，不需你有特殊能力以察觉目标是否死亡，也不会被假死能力欺骗，但复活类能力，包括死亡后触发的那些效果能正常运作，并正常让你尝试开启。自身珍重的人原则上取决于扮演，ST有裁定权。
-补充7：原则上，在轮回之境中，除非ST予以特别准许，否则不能进行以XP主动解锁之外的解锁形式，以避免什么召唤一个不稳定的怪殴打全队之类的事件。
-补充8：失去意识的角色不会满足上述开启本能觉醒的条件
-补充9：若玩家处于绝对不可能真正死亡的环境下，通常是无法开启本能觉醒的 ，除非玩家自身并不知晓，ST可以裁定这点。在一些虚拟环境下也同样如此（举例而言，前述战斗就是虚拟了一个玩家进入了刀剑神域用的实际上并非自己的身体）
-超常表现：
-首次开启本能觉醒的玩家一般会有超常表现奖励。
-超常表现代表了人物在潜能爆发之下做出的惊人举动，一般可以在以下范畴内进行选择：
-无视实力差距，一击秒杀对手。（视情况，ST可能将其降级为攻击骰全部取10但无加骰）
-一个行动无需检定，直接成功。（视情况，ST可能将其降级为检定骰全部取10但无加骰）
-免除本次伤害。
-将重伤的队友从敌人的包围中带出，期间片叶不沾身。
-一个超常表现只能被另一个超常表现抵消。
-ST也可以根据剧情与设定，额外增减超常表现的内容。</t>
+        <t xml:space="preserve">注：開啟本能覺醒檢定雖然名為檢定，但是不受到任何增加檢定結果，或者檢定DP能力的影響，除非特別說明。
+注：開啟本能覺醒只有在未開啟對應階段的本能覺醒狀態下才可以開啟，無論是出於主動還是被動的情況下。
+注：【當你已經可以開啟相應階段的本能覺醒時】，若再次達成開啟本能覺醒的條件，則【自動開啟】對應階段的本能覺醒。（如你擁有2階的本能覺醒，之後你因一次傷害受到了惡性傷害，則你立即自動開啟2階本能覺醒）
+開啟本能覺醒的條件包括：
+1）自身受到實際傷害，且結算該實際傷害後，導致自身的生命槽已經全部填滿，且最嚴重的是惡性時。
+2）自身受到足以致死的傷害或效果時。
+3）自身珍重的人或者隊友，造人受到致死傷害時。（ST應當根據RP來決定人，隊友或造人是否被珍視）
+4）自身因任意不良狀態點數，進入該點數對應的嚴重後果時。
+5）自身因任意不良狀態點數，進入該點數對應的毀滅後果時。
+6）自身全神灌注做一件非常緊急且重要的事情時。（此條ST選開）
+補充1：無論如何，受到衝擊傷害無法開啟本能覺醒。
+補充2：當玩家處於生命值上限減少的狀態時，計算條件按照當前的生命值上限來計算。
+補充3：任何自自殘技能或者招式等類似能力無法讓你開啟本能覺醒，哪怕會讓你死亡。
+補充4：無論任何條件，隊友以及友軍等類似的誤傷或者有意的行為，不得讓你開啟本能覺醒。
+補充5：每條每場景只會觸發一次，反覆治療或者降低不良狀態點數不會額外獲得開啟機會，但4,5條針對每種負面狀態一次。
+補充5：若一次效果會觸發多條，那麼你有多個開啟機會（例如你受到一個效果同時將你兩個負面狀態從輕度直接打進毀滅，你就有4次開啟機會。）
+補充6：隊友的致死傷害只需其在你敏感視覺範圍內，規則上死亡，不需你有特殊能力以察覺目標是否死亡，也不會被假死能力欺騙，但復活類能力，包括死亡後觸發的那些效果能正常運作，並正常讓你嘗試開啟。自身珍重的人原則上取決於扮演，ST有裁定權。
+補充7：原則上，在輪迴之境中，除非ST予以特別准許，否則不能進行以XP主動解鎖之外的解鎖形式，以避免什麼召喚一個不穩定的怪毆打全隊之類的事件。
+補充8：失去意識的角色不會滿足上述開啟本能覺醒的條件
+補充9：若玩家處於絕對不可能真正死亡的環境下，通常是無法開啟本能覺醒的 ，除非玩家自身並不知曉，ST可以裁定這點。在一些虛擬環境下也同樣如此（舉例而言，前述戰鬥就是虛擬了一個玩家進入了刀劍神域用的實際上並非自己的身體）
+超常表現：
+首次開啟本能覺醒的玩家一般會有超常表現獎勵。
+超常表現代表了人物在潛能爆發之下做出的驚人舉動，一般可以在以下範疇內進行選擇：
+無視實力差距，一擊秒殺對手。（視情況，ST可能將其降級為攻擊骰全部取10但無加骰）
+一個行動無需檢定，直接成功。（視情況，ST可能將其降級為檢定骰全部取10但無加骰）
+免除本次傷害。
+將重傷的隊友從敵人的包圍中帶出，期間片葉不沾身。
+一個超常表現只能被另一個超常表現抵消。
+ST也可以根據劇情與設定，額外增減超常表現的內容。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AG147">
       <text>
-        <t xml:space="preserve">人物可以把最大负重的东西举过头顶。可以暂时把最大负重两倍的物品抬离地面，人物可以推动和拖行的最大重量是最大负重的五倍。
-当你处于轻度负重时，你可以如常行动，不会受到负重影响。
-当你处于中度负重时，你每移动1米需要耗费2米移动力。
-当你处于重度负重时，你每移动1米需要耗费2米移动力，同时你进行的力量与敏捷相关检定失去一半自然成功数。
-当你处于超过重度负重的状态时，一般被称之为压垮，压垮不是负面状态，不可清除（除非造成该状态的物品被挪走，让你当前的负重下降或者使你自身的负重能力提升）。
-处于压垮状态下，你无法进行移动（这不代表你失去移动动作），你进行的力量和敏捷相关检定直接失败，你失去基础防御和闪避防御，以及传奇敏捷带来的防御附加成功。
-特殊：若没有特殊说明，则一般资源中的物品和装备的重量都是默认为中型体型适用的，若其变为大型体型的，则每上升1级，则重量*2。若其变为小型体型的，则每下降1级，则重量减半。</t>
+        <t xml:space="preserve">人物可以把最大負重的東西舉過頭頂。可以暫時把最大負重兩倍的物品抬離地面，人物可以推動和拖行的最大重量是最大負重的五倍。
+當你處於輕度負重時，你可以如常行動，不會受到負重影響。
+當你處於中度負重時，你每移動1米需要耗費2米移動力。
+當你處於重度負重時，你每移動1米需要耗費2米移動力，同時你進行的力量與敏捷相關檢定失去一半自然成功數。
+當你處於超過重度負重的狀態時，一般被稱之為壓垮，壓垮不是負面狀態，不可清除（除非造成該狀態的物品被挪走，讓你當前的負重下降或者使你自身的負重能力提升）。
+處於壓垮狀態下，你無法進行移動（這不代表你失去移動動作），你進行的力量和敏捷相關檢定直接失敗，你失去基礎防禦和閃避防禦，以及傳奇敏捷帶來的防禦附加成功。
+特殊：若沒有特殊說明，則一般資源中的物品和裝備的重量都是默認為中型體型適用的，若其變為大型體型的，則每上升1級，則重量*2。若其變為小型體型的，則每下降1級，則重量減半。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B115">
       <text>
-        <t xml:space="preserve">注意：快速整备功能需要在你的回合刚开始并且未进行过任何行动时才能进行，当快速整备功能使用过后，你的回合会被直接跳过；如果你在自己的回合时已经进行过任何消耗除自由动作以外的其他动作的行动，你无法进行快速整备，哪怕你拥有更多动作。
-注意：所有存放在仓库内的技能，必须是你满足其前提条件可以习得的，比如你没有施法者等级就无法储存法术。
-注意：一旦你将该资源储存起来，就视为你没有该资源，所以该资源也无法成为其他资源的前提。如A技能的前提是B技能，你将B技能存储起来，那么A技能则无法使用。
-注意：若你拥有储存技能或者类似的能力，一旦你将已经储存好的技能通过书签储存起来，那么由于视为你没有学习过该技能，所以你也无法将原本储存好的技能储存，原本储存的技能直接消失。
-注意：当你储存该技能的时候，该技能所带来的一切效果都将立即结束，无论是增益还是减益。
-注意：无论如何，能量池的基本用法以及赠送所得的资源无法储存。
-注意：任何拥有使用次数的技能若被储存，一旦该资源被配置后且其次数不为满，则该技能在其使用次数恢复至满值前，将无法被整备（次数小到包括一场景一次，大到包括一生一次。）,只有在其使用次数恢复，或者冷却时间结束时，才能被书签整备。
-注意：存在冷却时间的技能（大到使用后需要冷却10回合，小到只需要冷却一回合）同样被归于“拥有使用次数”，因此这类技能如果处于冷却时间中，或者次数不为满，则也遵循上述说明。
-注意：任何使用过后会对自己产生负面影响或者支付某类持续存在的代价的能力（例如“对自己造成10点晕眩点数”、“使用过后会使自己的攻击检定承受6DP无名减值”或者其他诸如此类的负面效果），在其持续时间尚未结束时，无法进行整备。
-注意：研发，升阶等类似的情况下，若你将对应的技能进行储存，则再次配置的时候，其依然是研发和升阶之后的状态，你无需为其再次投入资源。
-注意：当你进行洗点时，你可以将所有储存在仓库中的分数全部洗出来，但是购买书签本身的分数不会洗出来。
-注意：书签无法储存使用经验（XP）习得的技能。
-特殊：本资源可以重复购买，每次获得一页。
-特殊：时间轮回倒转等能力不会影响你已经配置好的技能，你不会因为时间倒流而回到之前的配置状态，除非你自己重新配置。 </t>
+        <t xml:space="preserve">注意：快速整備功能需要在你的回合剛開始並且未進行過任何行動時才能進行，當快速整備功能使用過後，你的回合會被直接跳過；如果你在自己的回合時已經進行過任何消耗除自由動作以外的其他動作的行動，你無法進行快速整備，哪怕你擁有更多動作。
+注意：所有存放在倉庫內的技能，必須是你滿足其前提條件可以習得的，比如你沒有施法者等級就無法儲存法術。
+注意：一旦你將該資源儲存起來，就視為你沒有該資源，所以該資源也無法成為其他資源的前提。如A技能的前提是B技能，你將B技能存儲起來，那麼A技能則無法使用。
+注意：若你擁有儲存技能或者類似的能力，一旦你將已經儲存好的技能通過書籤儲存起來，那麼由於視為你沒有學習過該技能，所以你也無法將原本儲存好的技能儲存，原本儲存的技能直接消失。
+注意：當你儲存該技能的時候，該技能所帶來的一切效果都將立即結束，無論是增益還是減益。
+注意：無論如何，能量池的基本用法以及贈送所得的資源無法儲存。
+注意：任何擁有使用次數的技能若被儲存，一旦該資源被配置後且其次數不為滿，則該技能在其使用次數恢復至滿值前，將無法被整備（次數小到包括一場景一次，大到包括一生一次。）,只有在其使用次數恢復，或者冷卻時間結束時，才能被書籤整備。
+注意：存在冷卻時間的技能（大到使用後需要冷卻10回合，小到只需要冷卻一回合）同樣被歸於“擁有使用次數”，因此這類技能如果處於冷卻時間中，或者次數不為滿，則也遵循上述說明。
+注意：任何使用過後會對自己產生負面影響或者支付某類持續存在的代價的能力（例如“對自己造成10點暈眩點數”、“使用過後會使自己的攻擊檢定承受6DP無名減值”或者其他諸如此類的負面效果），在其持續時間尚未結束時，無法進行整備。
+注意：研發，升階等類似的情況下，若你將對應的技能進行儲存，則再次配置的時候，其依然是研發和升階之後的狀態，你無需為其再次投入資源。
+注意：當你進行洗點時，你可以將所有儲存在倉庫中的分數全部洗出來，但是購買書籤本身的分數不會洗出來。
+注意：書籤無法儲存使用經驗（XP）習得的技能。
+特殊：本資源可以重複購買，每次獲得一頁。
+特殊：時間輪迴倒轉等能力不會影響你已經配置好的技能，你不會因為時間倒流而回到之前的配置狀態，除非你自己重新配置。 </t>
       </text>
     </comment>
     <comment authorId="0" ref="C49">
@@ -1211,75 +1211,75 @@
     </comment>
     <comment authorId="0" ref="B16">
       <text>
-        <t xml:space="preserve">九项属性代表了角色自身具有的能力，这些能力基于天生，并且可以后天锻炼，或者用来自轮回之境的各项资源进行强化。
-任何生物的每一项属性值都至少为1。
-角色的绝大多数行为都需要依据自身的属性，因此属性就相当于角色的主动能力和行为的可能性，并且有时也等同于你保持自身不被干扰或侵害的能力。
-若角色拥有某种超自然的本质或特性，属性也可能以超自然的形式发生作用。
-属性值表示人物在这一方面的能力如何。
-一般而言，属性值2-3是现代人类的平均水准，而属性值5差不多是正常人类所能达到的极限。从属性值6开始，角色获得了超越凡人的力量，达到了传说中英雄们的水准，而属性超过15的人则踏入了半神的领域，超过25之后，在凡人眼中他们就是神祗一般的存在了。
-首先，将人物的所有属性基本值设置为2。
-将3点/2点/1点的点数按照这自身意愿任意分别分配给生理、心智、互动三类属性（你可以将3点分配给生理系属性，也可以将这3点分配给心智系属性），然后将点数加在各项属性上。然后，将6点自由点数任意加在想要提高的属性上。另外，将一项已经加到4的属性提升到5，需要耗费2点点数，若没有特殊说明，则无法在建卡的时候将属性突破5点。</t>
+        <t xml:space="preserve">九項屬性代表了角色自身具有的能力，這些能力基於天生，並且可以後天鍛鍊，或者用來自輪迴之境的各項資源進行強化。
+任何生物的每一項屬性值都至少為1。
+角色的絕大多數行為都需要依據自身的屬性，因此屬性就相當於角色的主動能力和行為的可能性，並且有時也等同於你保持自身不被幹擾或侵害的能力。
+若角色擁有某種超自然的本質或特性，屬性也可能以超自然的形式發生作用。
+屬性值表示人物在這一方面的能力如何。
+一般而言，屬性值2-3是現代人類的平均水準，而屬性值5差不多是正常人類所能達到的極限。從屬性值6開始，角色獲得了超越凡人的力量，達到了傳說中英雄們的水準，而屬性超過15的人則踏入了半神的領域，超過25之後，在凡人眼中他們就是神祗一般的存在了。
+首先，將人物的所有屬性基本值設置為2。
+將3點/2點/1點的點數按照這自身意願任意分別分配給生理、心智、互動三類屬性（你可以將3點分配給生理系屬性，也可以將這3點分配給心智系屬性），然後將點數加在各項屬性上。然後，將6點自由點數任意加在想要提高的屬性上。另外，將一項已經加到4的屬性提升到5，需要耗費2點點數，若沒有特殊說明，則無法在建卡的時候將屬性突破5點。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AB7">
       <text>
-        <t xml:space="preserve">完好生命值是自动计算的。
-当完好生命值为负时，代表你需要转化伤势。</t>
+        <t xml:space="preserve">完好生命值是自動計算的。
+當完好生命值為負時，代表你需要轉化傷勢。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI39">
       <text>
-        <t xml:space="preserve">敏感范围：敏感范围是指角色可以清晰感觉到的范围，比如在这个范围之内角色可以清楚看到对面角色的面容，以及清晰听到他们的对话等，超出这个范围则无法看清楚目标身上的装饰，文字等。
-角色的敏感范围初始值为感知值*10米，一般情况下，大部分生物都是使用视觉才可以精确定位。
-若没有特殊能力的话，生物无法通过非视觉的能力进行定位。
-只有拥有“灵敏听觉”的生物才可以通过听觉在其敏感范围内进行模糊定位。
-只有拥有“灵敏嗅觉”的生物才可以通过嗅觉在其敏感范围内进行模糊定位。
-由于目标体积的区别（体积越大越容易被发现）所以在针对观察某一个目标时，敏感范围可能会进行动态的调整，调整的规则如下：
-目标的体积每比5大1，人物对该目标的敏感范围视为比原先提升10米，目标的体积每比5小 1，人物对该目标的敏感范围视为比原先降低10米。
-模糊范围：这个范围下，角色只能观察到那里有一个目标，但是无法看清楚样貌等其他信息，角色的模糊范围初始值为敏感范围*10米。一般而言，在没有特殊能力的情况下，模糊范围只有视距存在，一般说的视距也就是模糊范围。
-模糊范围下，角色可以如常对目标进行精确定位，但是无法进行细致的观察。
-特殊：由于角色的模糊范围因其自身的敏感范围所决定，所以改变其敏感范围的能力一般会同步影响其模糊范围。
-特殊：某些能力会给予角色感知超出敏感范围和模糊范围的感知能力，这会在对应的能力中做出说明。
-特殊：某些能力会提升单独某个感官的敏感范围或者模糊范围，比如望远镜可以提升视距，这些能力只将视觉范围扩大，并没有扩大敏感范围或者模糊范围本身。
+        <t xml:space="preserve">敏感範圍：敏感範圍是指角色可以清晰感覺到的範圍，比如在這個範圍之內角色可以清楚看到對面角色的面容，以及清晰聽到他們的對話等，超出這個範圍則無法看清楚目標身上的裝飾，文字等。
+角色的敏感範圍初始值為感知值*10米，一般情況下，大部分生物都是使用視覺才可以精確定位。
+若沒有特殊能力的話，生物無法通過非視覺的能力進行定位。
+只有擁有“靈敏聽覺”的生物才可以通過聽覺在其敏感範圍內進行模糊定位。
+只有擁有“靈敏嗅覺”的生物才可以通過嗅覺在其敏感範圍內進行模糊定位。
+由於目標體積的區別（體積越大越容易被發現）所以在針對觀察某一個目標時，敏感範圍可能會進行動態的調整，調整的規則如下：
+目標的體積每比5大1，人物對該目標的敏感範圍視為比原先提升10米，目標的體積每比5小 1，人物對該目標的敏感範圍視為比原先降低10米。
+模糊範圍：這個範圍下，角色只能觀察到那裡有一個目標，但是無法看清楚樣貌等其他信息，角色的模糊範圍初始值為敏感範圍*10米。一般而言，在沒有特殊能力的情況下，模糊範圍只有視距存在，一般說的視距也就是模糊範圍。
+模糊範圍下，角色可以如常對目標進行精確定位，但是無法進行細緻的觀察。
+特殊：由於角色的模糊範圍因其自身的敏感範圍所決定，所以改變其敏感範圍的能力一般會同步影響其模糊範圍。
+特殊：某些能力會給予角色感知超出敏感範圍和模糊範圍的感知能力，這會在對應的能力中做出說明。
+特殊：某些能力會提升單獨某個感官的敏感範圍或者模糊範圍，比如望遠鏡可以提升視距，這些能力只將視覺範圍擴大，並沒有擴大敏感範圍或者模糊範圍本身。
 </t>
       </text>
     </comment>
     <comment authorId="0" ref="B140">
       <text>
-        <t xml:space="preserve">戒指：戴在手指上的装备，一般穿脱是一个移动动作，每个角色有2个戒指位。</t>
+        <t xml:space="preserve">戒指：戴在手指上的裝備，一般穿脫是一個移動動作，每個角色有2個戒指位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="AV147">
       <text>
-        <t xml:space="preserve">你的体型每比中型大一级，则负重翻倍。
-如大型生物负重*2，超大型生物则负重*3，以此类推。
-你的体型每比中型小一级，则负重减半。
-如小型生物负重/2，微型生物则负重/3，以此类推。
-力量每增加1点，则轻度负重增加3公斤，同比中度负重的下限为轻载+1，上限为下限*2，重度为中度负重的上限+1，重度负重的上限为重度负重下线+（中载的上限-下限）。</t>
+        <t xml:space="preserve">你的體型每比中型大一級，則負重翻倍。
+如大型生物負重*2，超大型生物則負重*3，以此類推。
+你的體型每比中型小一級，則負重減半。
+如小型生物負重/2，微型生物則負重/3，以此類推。
+力量每增加1點，則輕度負重增加3公斤，同比中度負重的下限為輕載+1，上限為下限*2，重度為中度負重的上限+1，重度負重的上限為重度負重下線+（中載的上限-下限）。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI31">
       <text>
-        <t xml:space="preserve">体积：每个生物或者物体都占据着不同大下的空间，在本游戏中，一个0-0.33平方米的单位为体积1</t>
+        <t xml:space="preserve">體積：每個生物或者物體都佔據著不同大下的空間，在本遊戲中，一個0-0.33平方米的單位為體積1</t>
       </text>
     </comment>
     <comment authorId="0" ref="CO63">
       <text>
-        <t xml:space="preserve">基础防御：
-基础防御一般是指角色对攻击的基础反应，它意味着你招架，闪避。
-与其他加值不同，基础防御都是可以叠加的。</t>
+        <t xml:space="preserve">基礎防禦：
+基礎防禦一般是指角色對攻擊的基礎反應，它意味著你招架，閃避。
+與其他加值不同，基礎防禦都是可以疊加的。</t>
       </text>
     </comment>
     <comment authorId="0" ref="B132">
       <text>
-        <t xml:space="preserve">头盔：所有使用头部的装备，每个角色只有一个头盔位。</t>
+        <t xml:space="preserve">頭盔：所有使用頭部的裝備，每個角色只有一個頭盔位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="X24">
       <text>
-        <t xml:space="preserve">在风度相关的检定上获得n个附加成功。
-角色在进行本能觉醒的开启检定或任何机运骰检定时，在检定结果上+n，但是这不会让你获得机运骰的加骰。
-同时，你使用意志力的基础用法时，获得的完美加值提升2n点。</t>
+        <t xml:space="preserve">在風度相關的檢定上獲得n個附加成功。
+角色在進行本能覺醒的開啟檢定或任何機運骰檢定時，在檢定結果上+n，但是這不會讓你獲得機運骰的加骰。
+同時，你使用意志力的基礎用法時，獲得的完美加值提升2n點。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C33">
@@ -1295,63 +1295,63 @@
     </comment>
     <comment authorId="0" ref="CT63">
       <text>
-        <t xml:space="preserve">闪避防御：
-闪避加值一般加在防御或对抗范围效果的检定上，它意味着你灵活地左右躲闪，闪避加值一般只会加在防御上，也被称之为闪避防御。
-闪避防御不会叠加。</t>
+        <t xml:space="preserve">閃避防禦：
+閃避加值一般加在防禦或對抗範圍效果的檢定上，它意味著你靈活地左右躲閃，閃避加值一般只會加在防禦上，也被稱之為閃避防禦。
+閃避防禦不會疊加。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Q140">
       <text>
-        <t xml:space="preserve">戒指：戴在手指上的装备，一般穿脱是一个移动动作，每个角色有2个戒指位。</t>
+        <t xml:space="preserve">戒指：戴在手指上的裝備，一般穿脫是一個移動動作，每個角色有2個戒指位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CY63">
       <text>
-        <t xml:space="preserve">格挡防御：
-格挡防御只会加在防御上，它意味着你利用武器或自己的双手挡开敌人的攻击。
-格挡防御不会叠加。
+        <t xml:space="preserve">格擋防禦：
+格擋防禦只會加在防禦上，它意味著你利用武器或自己的雙手擋開敵人的攻擊。
+格擋防禦不會疊加。
 </t>
       </text>
     </comment>
     <comment authorId="0" ref="C25">
       <text>
-        <t xml:space="preserve">影响他人的能力，言行的感染力，煽动别人、让别人依你的想法行事的能力。
-任何能够表达自己意愿的存在都拥有操控值。
-任何操控值达到2或更高的个体，都应该具有某种明确、主动、自觉表达自己意图的手段，如语言。
-操控为0的人物会完全精神崩溃。他将会处于“昏迷”状态。</t>
+        <t xml:space="preserve">影響他人的能力，言行的感染力，煽動別人、讓別人依你的想法行事的能力。
+任何能夠表達自己意願的存在都擁有操控值。
+任何操控值達到2或更高的個體，都應該具有某種明確、主動、自覺表達自己意圖的手段，如語言。
+操控為0的人物會完全精神崩潰。他將會處於“昏迷”狀態。</t>
       </text>
     </comment>
     <comment authorId="0" ref="CP179">
       <text>
-        <t xml:space="preserve">本规则中，几乎所有的物品都是可以破坏的，包括玩家持有，占用装备位正在装备中的物品。只有无占位的物品可以获得更多保护，物品因为其可以被破坏的劣势而获得了额外特性。
-一般情况下，物品使用结构值（生命）代表物品被摧毁之前能承受的最大伤害。
-物品只有一条生命值，免疫原本造成冲击伤害的冲击伤害（这意味着伤害转化转化类能力对物品无效），同时其受到恶性伤害时，改为受到等额的严重伤害，当其受到不可避免的冲击伤害时，改为受到等额的不可避免的严重伤害。
-物件的硬度代表了这个物品有多……“耐打”。物品每次受到攻击时，会抵销掉相等于硬度值的伤害（详情请看“伤害类型”章节）。
-若一个物品未说明其生命值和硬度，默认其硬度为支线等级转化为D+分数/1000，因此一件A+4000的物品硬度为31。默认其结构值（生命值）为（硬度+体积）*3。没有特殊说明的物品一般不具备装甲值。
-如果用轮回之境兑换零件进行维修，则无需支线，将其分数/载具结构值，结果向上取整。每修复1点结构值则损耗对应的分数。
-修复：
-你现在可以维修对应的物品了。
-检定：智力+手艺-对应手艺子技能
-动作：这是一个周期性检定，周期为一小时，每当成功数到达其硬度，则恢复1点结构值。
-这意味着只要你潜心修理，则一定可以获得成功。
-需要注意的是，针对你所要修复的物品，你必须已经解读其图纸，并且相关属性和技能满足制造该物品的条件。</t>
+        <t xml:space="preserve">本規則中，幾乎所有的物品都是可以破壞的，包括玩家持有，佔用裝備位正在裝備中的物品。只有無佔位的物品可以獲得更多保護，物品因為其可以被破壞的劣勢而獲得了額外特性。
+一般情況下，物品使用結構值（生命）代表物品被摧毀之前能承受的最大傷害。
+物品只有一條生命值，免疫原本造成衝擊傷害的衝擊傷害（這意味著傷害轉化轉化類能力對物品無效），同時其受到惡性傷害時，改為受到等額的嚴重傷害，當其受到不可避免的衝擊傷害時，改為受到等額的不可避免的嚴重傷害。
+物件的硬度代表了這個物品有多……“耐打”。物品每次受到攻擊時，會抵銷掉相等於硬度值的傷害（詳情請看“傷害類型”章節）。
+若一個物品未說明其生命值和硬度，默認其硬度為支線等級轉化為D+分數/1000，因此一件A+4000的物品硬度為31。默認其結構值（生命值）為（硬度+體積）*3。沒有特殊說明的物品一般不具備裝甲值。
+如果用輪迴之境兌換零件進行維修，則無需支線，將其分數/載具結構值，結果向上取整。每修復1點結構值則損耗對應的分數。
+修復：
+你現在可以維修對應的物品了。
+檢定：智力+手藝-對應手藝子技能
+動作：這是一個週期性檢定，週期為一小時，每當成功數到達其硬度，則恢復1點結構值。
+這意味著只要你潛心修理，則一定可以獲得成功。
+需要注意的是，針對你所要修復的物品，你必須已經解讀其圖紙，並且相關屬性和技能滿足製造該物品的條件。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI48">
       <text>
-        <t xml:space="preserve">一阶本能觉醒：
-一阶本能觉醒的开启，意味着生物进化潜能的释放。从此，只要你需要，你就可以成为任何一个领域的天才。
-解开第一阶本能觉醒后，你可以解放远古人类时的战斗本能，你的智力决定了你引导战斗本能的能力，你的感知决定了你能动用多大程度的战斗本能，被动用的战斗本能将体现在你的集中力上。</t>
+        <t xml:space="preserve">一階本能覺醒：
+一階本能覺醒的開啟，意味著生物進化潛能的釋放。從此，只要你需要，你就可以成為任何一個領域的天才。
+解開第一階本能覺醒後，你可以解放遠古人類時的戰鬥本能，你的智力決定了你引導戰鬥本能的能力，你的感知決定了你能動用多大程度的戰鬥本能，被動用的戰鬥本能將體現在你的集中力上。</t>
       </text>
     </comment>
     <comment authorId="0" ref="Q132">
       <text>
-        <t xml:space="preserve">项链：戴在脖子上的装备，一般为魔幻本质特有，每个角色只有一个项链位。</t>
+        <t xml:space="preserve">項鍊：戴在脖子上的裝備，一般為魔幻本質特有，每個角色只有一個項鍊位。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BK48">
       <text>
-        <t xml:space="preserve">被动开启：任何时候，当你达成开启条件时（见上文说明），你将获得一次开启本能觉醒的机会。你投掷一个D10，若结果在10或10以上，则你成功开启了一阶本能觉醒。</t>
+        <t xml:space="preserve">被動開啟：任何時候，當你達成開啟條件時（見上文說明），你將獲得一次開啟本能覺醒的機會。你投擲一個D10，若結果在10或10以上，則你成功開啟了一階本能覺醒。</t>
       </text>
     </comment>
     <comment authorId="0" ref="C50">
@@ -1367,68 +1367,68 @@
     </comment>
     <comment authorId="0" ref="AH16">
       <text>
-        <t xml:space="preserve">专长定义了人物的一些特殊能力，它会让人物在某些行动中获益。这是一种训练，经验，天赋以及能力的体现。
-你可以使用经验值或者一些特殊的方法来提升专长。
-同时，你必须满足专长的“前提条件”才可以习得该专长。
-在建卡时，若你没有特殊说明，则无法选择任何战斗系专长。
-具体这些专长的功能以及作用和学习方法等内容，请看“专长概述”章节，这里只阐述如何创建角色时决定你的专长。
-首先，人物没有任何专长。
-将15点专长点数分配在普通专长上，每个普通专长都有其对应的等级，1级普通专长对应1点专长点数，2级普通专长对应2点专长点数，以此类推。
-一般而言，若没有特殊说明，专长必须从低级向高级习得，如习得一个3级普通专长，需要花费1+2+3，一共6点专长点数。有些专长只有高等级的部分，此时花费对应的专长点数即可，如习得一个只有2级和3级的普通专长时，则一共需要花费2+3点专长点数。
-若玩家拥有剩余的专长点数，则不会保留，直接浪费掉。
-玩家在建卡时，若想习得“战斗专长”，必须习得“特殊身份”专长。
-玩家在建卡时，无法习得“轮回之境专长”。</t>
+        <t xml:space="preserve">專長定義了人物的一些特殊能力，它會讓人物在某些行動中獲益。這是一種訓練，經驗，天賦以及能力的體現。
+你可以使用經驗值或者一些特殊的方法來提升專長。
+同時，你必須滿足專長的“前提條件”才可以習得該專長。
+在建卡時，若你沒有特殊說明，則無法選擇任何戰鬥系專長。
+具體這些專長的功能以及作用和學習方法等內容，請看“專長概述”章節，這裡只闡述如何創建角色時決定你的專長。
+首先，人物沒有任何專長。
+將15點專長點數分配在普通專長上，每個普通專長都有其對應的等級，1級普通專長對應1點專長點數，2級普通專長對應2點專長點數，以此類推。
+一般而言，若沒有特殊說明，專長必須從低級向高級習得，如習得一個3級普通專長，需要花費1+2+3，一共6點專長點數。有些專長只有高等級的部分，此時花費對應的專長點數即可，如習得一個只有2級和3級的普通專長時，則一共需要花費2+3點專長點數。
+若玩家擁有剩餘的專長點數，則不會保留，直接浪費掉。
+玩家在建卡時，若想習得“戰鬥專長”，必須習得“特殊身份”專長。
+玩家在建卡時，無法習得“輪迴之境專長”。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BN48">
       <text>
-        <t xml:space="preserve">主动开启：当你已经成功通过上述方法开启过一次一阶本能觉醒后，你便可以通过一个移动动作，并且支付1点意志力，来开启一阶本能觉醒，获得一阶本能觉醒的开启效果。</t>
+        <t xml:space="preserve">主動開啟：當你已經成功通過上述方法開啟過一次一階本能覺醒後，你便可以通過一個移動動作，並且支付1點意志力，來開啟一階本能覺醒，獲得一階本能覺醒的開啟效果。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI40">
       <text>
-        <t xml:space="preserve">意志力：人物的意志力代表人物凭自己的坚定意志扭转劣势或改变现实的能力。意志力是一个可以消耗以换取收益的点数，其初始上限为决心+沉着，建立新人卡时，人物的意志力为最大值。
-人物的意志力代表人物凭自己的坚定意志扭转劣势或改变现实的能力。 
-关于意志力的更多用法与回复，详见“意志力规则”页。</t>
+        <t xml:space="preserve">意志力：人物的意志力代表人物憑自己的堅定意志扭轉劣勢或改變現實的能力。意志力是一個可以消耗以換取收益的點數，其初始上限為決心+沉著，建立新人卡時，人物的意志力為最大值。
+人物的意志力代表人物憑自己的堅定意志扭轉劣勢或改變現實的能力。 
+關於意志力的更多用法與回覆，詳見“意志力規則”頁。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BQ48">
       <text>
-        <t xml:space="preserve">解除：解除一阶本能觉醒是一个自由动作。</t>
+        <t xml:space="preserve">解除：解除一階本能覺醒是一個自由動作。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BS48">
       <text>
-        <t xml:space="preserve">效果：当你处于解开一阶本能觉醒状态时，你可以将你传奇感知和传奇智力中较低者作为完美加值加到你的全检定以及防御上。
-你在使用意志力的基础用法时，可以获得等于感知和智力中较低者的完美加值。
-同时，你在使用任何技能时都视为拥有1/2级。也就是说，无论使用任何技能，你都视为拥有该技能一般而不会受到检定上的罚值，但不会获得来自技能等级的DP加值。
-这是来自于基因层面的记忆，因此不会被任何负面效果抵消。
-额外奖励：只有第一次，当成功开启一阶本能觉醒时，ST应当给予玩家一次超常表现奖励。</t>
+        <t xml:space="preserve">效果：當你處於解開一階本能覺醒狀態時，你可以將你傳奇感知和傳奇智力中較低者作為完美加值加到你的全檢定以及防禦上。
+你在使用意志力的基礎用法時，可以獲得等於感知和智力中較低者的完美加值。
+同時，你在使用任何技能時都視為擁有1/2級。也就是說，無論使用任何技能，你都視為擁有該技能一般而不會受到檢定上的罰值，但不會獲得來自技能等級的DP加值。
+這是來自於基因層面的記憶，因此不會被任何負面效果抵消。
+額外獎勵：只有第一次，當成功開啟一階本能覺醒時，ST應當給予玩家一次超常表現獎勵。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BX48">
       <text>
-        <t xml:space="preserve">持续时间：你每维持一轮本能觉醒需要花费1点意志力，当你意志力不足时直接关闭，你在你回合开始时决定是否花费意志力，若不花费则本能觉醒效果立即结束。</t>
+        <t xml:space="preserve">持續時間：你每維持一輪本能覺醒需要花費1點意志力，當你意志力不足時直接關閉，你在你回合開始時決定是否花費意志力，若不花費則本能覺醒效果立即結束。</t>
       </text>
     </comment>
     <comment authorId="0" ref="BI32">
       <text>
-        <t xml:space="preserve">根据以下表格中的体积来决定单位的体型。
-体型：超微型、微型、小型、中型、大型、超大型、巨型、超巨型
-体积：忽略不计、1、2-3、4-6、7-12、13-21、22-33、34以上
-占据空间（直立）：无、半格（1平方米）、1格（2平方米）、1格（2平方米）、 2格（4平方米）、3格（6平方米）、4格（8平方米）、6格（12平米）以上
-范例：蚊子、麻雀、山猫、人类、肿头龙、大象、三角龙、蓝鲸
-生命值调整：0、1、2、5、10、17、26、37以上
-触及：无、无、2米、2米、2米、4米、6米、8米以上
-基础速度修正：无、1米、2米、5米、5米、8米、12米、16米以上
-普通成年人体积为5，也就是中型生物。</t>
+        <t xml:space="preserve">根據以下表格中的體積來決定單位的體型。
+體型：超微型、微型、小型、中型、大型、超大型、巨型、超巨型
+體積：忽略不計、1、2-3、4-6、7-12、13-21、22-33、34以上
+佔據空間（直立）：無、半格（1平方米）、1格（2平方米）、1格（2平方米）、 2格（4平方米）、3格（6平方米）、4格（8平方米）、6格（12平米）以上
+範例：蚊子、麻雀、山貓、人類、腫頭龍、大象、三角龍、藍鯨
+生命值調整：0、1、2、5、10、17、26、37以上
+觸及：無、無、2米、2米、2米、4米、6米、8米以上
+基礎速度修正：無、1米、2米、5米、5米、8米、12米、16米以上
+普通成年人體積為5，也就是中型生物。</t>
       </text>
     </comment>
     <comment authorId="0" ref="X25">
       <text>
-        <t xml:space="preserve">在操控相关的检定上获得n个附加成功。
-角色每场景获得n次重骰机会，可以在投骰结束后对结果不满意再使用，取较好的结果。（注意本能力重投的是骰子，不是检定，针对不是检定的能力，该效果依然可以生效，但是针对不能重投的能力，本能力无法起效），若该次投骰是检定，则该次检定获得n*3DP完美加值。
-特殊的是：本传奇属性可以对处于同一场景的自愿目标生效。</t>
+        <t xml:space="preserve">在操控相關的檢定上獲得n個附加成功。
+角色每場景獲得n次重骰機會，可以在投骰結束後對結果不滿意再使用，取較好的結果。（注意本能力重投的是骰子，不是檢定，針對不是檢定的能力，該效果依然可以生效，但是針對不能重投的能力，本能力無法起效），若該次投骰是檢定，則該次檢定獲得n*3DP完美加值。
+特殊的是：本傳奇屬性可以對處於同一場景的自願目標生效。</t>
       </text>
     </comment>
   </commentList>
@@ -1471,7 +1471,7 @@
     <t>陂腳（-1）</t>
   </si>
   <si>
-    <t>描述：你腦子裡的好像有一塊精准的表。
+    <t>描述：你腦子裡的好像有一塊精準的表。
  你總是知道現在是什麼時候，精度以秒計算。你可以以同樣的精度測算經過的時間長度。時區變化或者打瞌睡都不會影響此能力，你可以在你事先選定的時間點醒過來。時空的變換不會影響你。你總是在絕對的意義上知道當前的時間，當你在時空中旅行，ST會告訴你“你向過去行進了92876.3天”，並令你——或其它人——自行解決類似“那TM閏年怎麼計算啊？”的問題。</t>
   </si>
   <si>
@@ -1601,7 +1601,7 @@
     <t>玻璃人（-5）</t>
   </si>
   <si>
-    <t>描述：你可以將你的眼睛聚焦，如同使用了望遠鏡。 
+    <t>描述：你可以將你的眼睛聚焦，如同使用瞭望遠鏡。 
  你可以在模糊範圍內進行特定部位攻擊。</t>
   </si>
   <si>
@@ -1613,7 +1613,7 @@
   <si>
     <t>描述：你的身體因為嚴重疾病變得如同玻璃一般脆弱，稍微的碰撞都會使你骨折。 
  每當你受到傷害時，你的隨機一條肢體都會獲得相當於所受傷害的不可疊加的肢體妨害點數，強韌豁免。並且你清除肢體妨害點數的難度是原本的兩倍，這意味著你清除肢體妨害點數時，假設原本需要1點成功數可以降低1點，則現在需要2點成功數。 
- 說明：需要注意的是，這只影響清除時的難度，不影響獲得時的豁免檢定。</t>
+ 說明：需要注意的是，這隻影響清除時的難度，不影響獲得時的豁免檢定。</t>
   </si>
   <si>
     <t>描述：你重病的次數屈指可數。 
@@ -1728,7 +1728,7 @@
     <t>病嬌（1）</t>
   </si>
   <si>
-    <t>描述：你對你喜歡的存在愛到癡狂，想要將其永遠獨佔。
+    <t>描述：你對你喜歡的存在愛到痴狂，想要將其永遠獨佔。
  你設置1至3個外貌或心理上的特點（如“白髮”“溫柔”）。
  你對符合其中至少一項的目標進行的追蹤無需判定自動成功。</t>
   </si>
@@ -1750,14 +1750,14 @@
     <t>擁有“無助”缺陷</t>
   </si>
   <si>
-    <t>描述：你是只為復仇而活的復仇鬼。
+    <t>描述：你是隻為復仇而活的復仇鬼。
  “無助”的效果改為，當你視覺線內的友方因攻擊而昏迷或死亡時，你對導致其昏迷或死亡的目標的攻擊檢定獲得3DP表現加值，傷害上限提升3點，持續至目標死亡為止。</t>
   </si>
   <si>
     <t>絕對音感（2）</t>
   </si>
   <si>
-    <t>不能擁有“音癡”缺陷</t>
+    <t>不能擁有“音痴”缺陷</t>
   </si>
   <si>
     <t>描述：你天生就擁有對於音樂和音符的絕對感受力。
@@ -1942,7 +1942,7 @@
   <si>
     <t>描述：你受傷就會流血，而且流血不止。 
  每當你受到傷害時，你都會獲得相當於所受傷害的不可疊加的流血點數，並且你清除流血點數是原本的兩倍，這意味著你清除流血點數時，假設原本需要1點成功數可以降低1點，則現在需要2點成功數。 
- 說明：需要注意的是，這只影響清除時的難度，不影響獲得時的豁免檢定。</t>
+ 說明：需要注意的是，這隻影響清除時的難度，不影響獲得時的豁免檢定。</t>
   </si>
   <si>
     <t>近親傳承（-1）</t>
@@ -2042,7 +2042,7 @@
     <t>獨來獨往（-2）</t>
   </si>
   <si>
-    <t>描述：你出身于海盜、土匪或其他類似習慣于插兄弟肋骨兩刀的環境，你已經習慣什麼事情都只依靠自己。盟友的存在會很容易讓你分心，你需要擁有只屬於你自己的空間才能將事情做到最好。
+    <t>描述：你出身於海盜、土匪或其他類似習慣於插兄弟肋骨兩刀的環境，你已經習慣什麼事情都只依靠自己。盟友的存在會很容易讓你分心，你需要擁有隻屬於你自己的空間才能將事情做到最好。
  效果：你和盟友一同行動時，你的全檢定承受2DP減值。
  特殊：由於本缺憾會影響玩家集體行動導致分團而影響劇情，甚至會影響PC團結，所以ST有權禁用本缺憾。</t>
   </si>
@@ -2174,10 +2174,10 @@
  若你拒絕，則你失去全部剩餘意志力，並且接下來的冒險世界中你無法恢復意志力。</t>
   </si>
   <si>
-    <t>色欲（-1）</t>
-  </si>
-  <si>
-    <t>描述：你總是執著於男女之間的情欲，對於異性你總是抱有著一種異樣的看法。
+    <t>色慾（-1）</t>
+  </si>
+  <si>
+    <t>描述：你總是執著於男女之間的情慾，對於異性你總是抱有著一種異樣的看法。
  效果：你在對於與你性別不同的人物進行互動系技能的相關檢定承受2DP減值。</t>
   </si>
   <si>
@@ -2293,7 +2293,7 @@
  你在劇情世界中使用貨品和服務時會多花費10％的貨幣作為額外享受的消耗（而且不能由盟友支付），在防止饑餓和口渴時你須要正常2倍的食物和飲料。</t>
   </si>
   <si>
-    <t>花癡（-1）</t>
+    <t>花痴（-1）</t>
   </si>
   <si>
     <t>描述：你的整個腦部都被另一個人的身影所佔據，當你遠離它時你會陷入沮喪。 
@@ -2310,7 +2310,7 @@
     <t>不注意周圍（-1）</t>
   </si>
   <si>
-    <t>描述：不管是你喜歡做白日夢還是習慣於將一切都交托於他人，總之你從不注意你周圍的環境和其他人。 
+    <t>描述：不管是你喜歡做白日夢還是習慣於將一切都交託於他人，總之你從不注意你周圍的環境和其他人。 
  你的察言觀色和基於視覺的偵查檢定承受4DP減值。</t>
   </si>
   <si>
@@ -2339,7 +2339,7 @@
   </si>
   <si>
     <t>描述：你非常害怕公眾、群體或重要人物（如你的騎士團、你的領主、你的家人或你的愛人）知道你的不可告人的恥辱真相。 
- 你與ST共同定制一個你的恥辱過去（如被哥布林抓走之類的），你在對抗恐懼點數的豁免檢定中承受3DP減值，你在對抗任何脅迫的相關檢定時，承受3DP減值。如果你有對恐懼點數免疫的能力，那麼你不用受到這些懲罰，而是失去對恐懼點數的免疫能力（無論其來源如何）。如果他人得知了你的恥辱過去，則你對那個人的互動系檢定承受3DP減值。</t>
+ 你與ST共同定製一個你的恥辱過去（如被哥布林抓走之類的），你在對抗恐懼點數的豁免檢定中承受3DP減值，你在對抗任何脅迫的相關檢定時，承受3DP減值。如果你有對恐懼點數免疫的能力，那麼你不用受到這些懲罰，而是失去對恐懼點數的免疫能力（無論其來源如何）。如果他人得知了你的恥辱過去，則你對那個人的互動系檢定承受3DP減值。</t>
   </si>
   <si>
     <t>怕黑（-1）</t>
@@ -2374,7 +2374,7 @@
  所有動物對你的初始態度下降一級，並且對你態度為不為敵對的自然本質的動物們不會自願近接你的10米之內，除非你或那動物的主人成功通過DC 10的馴養動物、騎乘戰鬥或改善動物態度。</t>
   </si>
   <si>
-    <t>污穢烙印（-1）</t>
+    <t>汙穢烙印（-1）</t>
   </si>
   <si>
     <t>描述：你的血肉上天生烙有一個邪惡的印記，其可能來自超越心智的恐怖。 
@@ -2387,18 +2387,18 @@
     <t>神隱（-2）</t>
   </si>
   <si>
-    <t>描述：當你還是一個孩子時，你曾被神秘的存在拐走了一段時間。當你回來以後，你仍對那段經歷念念不忘。你渴望回到那個地方，並覺得凡人的世界如此沉悶而令人作嘔，所以你平時毫無食欲，並且對各種奇怪景象視若無睹。 
+    <t>描述：當你還是一個孩子時，你曾被神秘的存在拐走了一段時間。當你回來以後，你仍對那段經歷念念不忘。你渴望回到那個地方，並覺得凡人的世界如此沉悶而令人作嘔，所以你平時毫無食慾，並且對各種奇怪景象視若無睹。 
  效果：你對抗疾病、幻覺和所有類型的毒藥的豁免承受3DP減值。你對抗妖怪施放的法術、能力和技能進行的豁免承受3DP減值。</t>
   </si>
   <si>
-    <t>路癡（-1）</t>
+    <t>路痴（-1）</t>
   </si>
   <si>
     <t>描述：你完全沒有方向感，在直路上都能迷路。 
  你的追蹤檢定自動失敗，當你和你的隊友分頭行動時，你無法通過移動的方式主動和隊友匯合。</t>
   </si>
   <si>
-    <t>音癡（-2）</t>
+    <t>音痴（-2）</t>
   </si>
   <si>
     <t>描述：你對音樂本身完全沒有一點感覺。 
@@ -2427,10 +2427,10 @@
  當你在戰鬥中乘坐載具時，你每輪結束時投一個D2，如果結果為2，則你乘坐的載具癱瘓至戰鬥結束。</t>
   </si>
   <si>
-    <t>機械白癡（-4）</t>
-  </si>
-  <si>
-    <t>描述：你完全就不會操作電子設備，任何你打算使用的電器都會在你手中損壞。你擁有人稱“機械白癡”的體質。
+    <t>機械白痴（-4）</t>
+  </si>
+  <si>
+    <t>描述：你完全就不會操作電子設備，任何你打算使用的電器都會在你手中損壞。你擁有人稱“機械白痴”的體質。
  效果：你使用任何科技本質的物品，或消耗電力的物品時，你骰一個D10，如果結果不為10，物品發生故障在1分鐘內無法使用，如果結果為10，物品被摧毀。</t>
   </si>
   <si>
@@ -2868,7 +2868,7 @@
     <t>能量池/刻度</t>
   </si>
   <si>
-    <t>总上限</t>
+    <t>總上限</t>
   </si>
   <si>
     <t>不良狀態/其他效果</t>
@@ -3154,7 +3154,7 @@
     </r>
   </si>
   <si>
-    <t>夜视（1）</t>
+    <t>夜視（1）</t>
   </si>
   <si>
     <t>外貌/特徵</t>
@@ -3169,7 +3169,7 @@
     <t>衝擊</t>
   </si>
   <si>
-    <t>关键抵抗屬性</t>
+    <t>關鍵抵抗屬性</t>
   </si>
   <si>
     <t>顏料</t>
@@ -3193,7 +3193,7 @@
     <t>溫和，善於傾聽，對大部分的人都一視同仁</t>
   </si>
   <si>
-    <t>完美形体（3）</t>
+    <t>完美形體（3）</t>
   </si>
   <si>
     <t>惡性</t>
@@ -3217,7 +3217,7 @@
     <t>基礎屬性</t>
   </si>
   <si>
-    <t>绝处逢生（9）</t>
+    <t>絕處逢生（9）</t>
   </si>
   <si>
     <t>屬性加值</t>
@@ -3271,7 +3271,7 @@
     <t>專長名稱</t>
   </si>
   <si>
-    <t>等级</t>
+    <t>等級</t>
   </si>
   <si>
     <t>鮮明特點</t>
@@ -3287,7 +3287,7 @@
     <t>力量</t>
   </si>
   <si>
-    <t>强迫症（-2）</t>
+    <t>強迫症（-2）</t>
   </si>
   <si>
     <t>精神力天賦</t>
@@ -3311,7 +3311,7 @@
     <t>異能者</t>
   </si>
   <si>
-    <t>独来独往（-2）</t>
+    <t>獨來獨往（-2）</t>
   </si>
   <si>
     <t>心智</t>
@@ -3332,7 +3332,7 @@
     <t>感知</t>
   </si>
   <si>
-    <t>基础屬性</t>
+    <t>基礎屬性</t>
   </si>
   <si>
     <t>忍耐力</t>
@@ -3344,7 +3344,7 @@
     <t>白冠之王</t>
   </si>
   <si>
-    <t>隐秘耻辱（-3）</t>
+    <t>隱秘恥辱（-3）</t>
   </si>
   <si>
     <t>暈車</t>
@@ -3376,7 +3376,7 @@
     <t>沉著</t>
   </si>
   <si>
-    <t>载具杀手（-4）</t>
+    <t>載具殺手（-4）</t>
   </si>
   <si>
     <t>泰拉人(4)</t>
@@ -3385,7 +3385,7 @@
     <t>技能</t>
   </si>
   <si>
-    <t>基本等级</t>
+    <t>基本等級</t>
   </si>
   <si>
     <t>專業/子項</t>
@@ -3406,7 +3406,7 @@
     <t>施法天才(1)</t>
   </si>
   <si>
-    <t>其他来源</t>
+    <t>其他來源</t>
   </si>
   <si>
     <t>檢定項目</t>
@@ -3457,7 +3457,7 @@
     <t>增壓法術(1)</t>
   </si>
   <si>
-    <t>机械白痴（-4）</t>
+    <t>機械白痴（-4）</t>
   </si>
   <si>
     <t>傾城之貌(1-5)</t>
@@ -3538,7 +3538,7 @@
     <t>旅行速度</t>
   </si>
   <si>
-    <t>凝血功能障碍（-5）</t>
+    <t>凝血功能障礙（-5）</t>
   </si>
   <si>
     <t>求生</t>
@@ -3604,7 +3604,7 @@
     <t>觸及範圍</t>
   </si>
   <si>
-    <t>基础速度</t>
+    <t>基礎速度</t>
   </si>
   <si>
     <t>調查</t>
@@ -3637,7 +3637,7 @@
     <t>急救</t>
   </si>
   <si>
-    <t>检定值</t>
+    <t>檢定值</t>
   </si>
   <si>
     <t>護理</t>
@@ -3652,7 +3652,7 @@
     <t>手術</t>
   </si>
   <si>
-    <t>基础防御</t>
+    <t>基礎防禦</t>
   </si>
   <si>
     <t>攻擊名稱</t>
@@ -3697,7 +3697,7 @@
     <t>反射豁免</t>
   </si>
   <si>
-    <t>触及范围</t>
+    <t>觸及範圍</t>
   </si>
   <si>
     <t>互　動　系</t>
@@ -3718,7 +3718,7 @@
     <t>強韌豁免</t>
   </si>
   <si>
-    <t>敏感范围</t>
+    <t>敏感範圍</t>
   </si>
   <si>
     <t>儀式(3)</t>
@@ -3727,7 +3727,7 @@
     <t>感受</t>
   </si>
   <si>
-    <t>堅定立場(决心/沉着取高)</t>
+    <t>堅定立場(決心/沉著取高)</t>
   </si>
   <si>
     <t>心靈檢定</t>
@@ -3745,7 +3745,7 @@
     <t>被動特殊能力提醒與備註</t>
   </si>
   <si>
-    <t>额外</t>
+    <t>額外</t>
   </si>
   <si>
     <t>互 動</t>
@@ -3757,7 +3757,7 @@
     <t>表達</t>
   </si>
   <si>
-    <t>一阶</t>
+    <t>一階</t>
   </si>
   <si>
     <t>被動開啟</t>
@@ -3778,16 +3778,16 @@
     <t>自我保護(3)、察言觀色(4)</t>
   </si>
   <si>
-    <t>二阶</t>
+    <t>二階</t>
   </si>
   <si>
     <t>表達類</t>
   </si>
   <si>
-    <t>三阶</t>
-  </si>
-  <si>
-    <t>XP积累</t>
+    <t>三階</t>
+  </si>
+  <si>
+    <t>XP積累</t>
   </si>
   <si>
     <t>意志力獲得的完美加值+2</t>
@@ -3805,13 +3805,13 @@
     <t>威嚇</t>
   </si>
   <si>
-    <t>四阶</t>
+    <t>四階</t>
   </si>
   <si>
     <t>對敵人上鳶尾+2</t>
   </si>
   <si>
-    <t>心灵检定</t>
+    <t>心靈檢定</t>
   </si>
   <si>
     <t>交際</t>
@@ -3826,7 +3826,7 @@
     <t>收集情報</t>
   </si>
   <si>
-    <t>五阶</t>
+    <t>五階</t>
   </si>
   <si>
     <t>掩飾</t>
@@ -3835,10 +3835,10 @@
     <t>唬騙/易容/偽裝</t>
   </si>
   <si>
-    <t>层级</t>
-  </si>
-  <si>
-    <t>开锁</t>
+    <t>層級</t>
+  </si>
+  <si>
+    <t>開鎖</t>
   </si>
   <si>
     <t>完美加值</t>
@@ -3854,10 +3854,10 @@
     <t>偽裝</t>
   </si>
   <si>
-    <t>本能觉醒</t>
-  </si>
-  <si>
-    <t>被动特殊能力提醒与备注</t>
+    <t>本能覺醒</t>
+  </si>
+  <si>
+    <t>被動特殊能力提醒與備註</t>
   </si>
   <si>
     <t>攻擊預設</t>
@@ -4053,7 +4053,7 @@
     <t>殞劍、施法檢定</t>
   </si>
   <si>
-    <t>强化分类</t>
+    <t>強化分類</t>
   </si>
   <si>
     <t>能力</t>
@@ -4098,7 +4098,7 @@
     <t>Ｄ</t>
   </si>
   <si>
-    <t>特性 請給你的特性也標注上等級</t>
+    <t>特性 請給你的特性也標註上等級</t>
   </si>
   <si>
     <t>承冠之重</t>
@@ -4140,10 +4140,10 @@
     <t>心靈溝通</t>
   </si>
   <si>
-    <t>修炼体系</t>
-  </si>
-  <si>
-    <t>称号与流派</t>
+    <t>修煉體系</t>
+  </si>
+  <si>
+    <t>稱號與流派</t>
   </si>
   <si>
     <t>注意：將你的書籤頁與其他能力分隔開來</t>
@@ -4162,10 +4162,10 @@
   </si>
   <si>
     <t>【2點全能量抗性】【法術抗力4】
-超级防护：穿戴者获得3点物理伤害吸收，每次吸收都需要消耗1点穿戴者的魔力。</t>
-  </si>
-  <si>
-    <t>储存支線</t>
+超級防護：穿戴者獲得3點物理傷害吸收，每次吸收都需要消耗1點穿戴者的魔力。</t>
+  </si>
+  <si>
+    <t>儲存支線</t>
   </si>
   <si>
     <t>配置支線</t>
@@ -4177,7 +4177,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>特性 请给你的特性也标注上等级</t>
+    <t>特性 請給你的特性也標註上等級</t>
   </si>
   <si>
     <t>飛衛學射(C)</t>
@@ -4189,7 +4189,7 @@
     <t>強生健體(D)</t>
   </si>
   <si>
-    <t>D级支線</t>
+    <t>D級支線</t>
   </si>
   <si>
     <t>自承牽挺(D)</t>
@@ -4201,13 +4201,13 @@
     <t>運動健將-自我保護(D)</t>
   </si>
   <si>
-    <t>C级支線</t>
-  </si>
-  <si>
-    <t>B级支線</t>
-  </si>
-  <si>
-    <t>盤游弋射(D)</t>
+    <t>C級支線</t>
+  </si>
+  <si>
+    <t>B級支線</t>
+  </si>
+  <si>
+    <t>盤遊弋射(D)</t>
   </si>
   <si>
     <t>人皇步(C)</t>
@@ -4216,7 +4216,7 @@
     <t>求勝意志(C)</t>
   </si>
   <si>
-    <t>A级支線</t>
+    <t>A級支線</t>
   </si>
   <si>
     <t>魔術師</t>
@@ -4228,7 +4228,7 @@
     <t>光明騎士</t>
   </si>
   <si>
-    <t>S级支線</t>
+    <t>S級支線</t>
   </si>
   <si>
     <t>視而後可(C)</t>
@@ -4327,7 +4327,7 @@
     <t>鞋襪位</t>
   </si>
   <si>
-    <t>于珊瑚島綻放之冰花（Ｂ）</t>
+    <t>於珊瑚島綻放之冰花（Ｂ）</t>
   </si>
   <si>
     <t>光之契約者（Ｃ）</t>
@@ -4372,19 +4372,19 @@
     <t>單位：公斤</t>
   </si>
   <si>
-    <t>技艺/招式/法术等主动特殊能力</t>
-  </si>
-  <si>
-    <t>手表插件：书签</t>
-  </si>
-  <si>
-    <t>举例</t>
+    <t>技藝/招式/法術等主動特殊能力</t>
+  </si>
+  <si>
+    <t>手錶插件：書籤</t>
+  </si>
+  <si>
+    <t>舉例</t>
   </si>
   <si>
     <t>獲得獎勵及支出-明細</t>
   </si>
   <si>
-    <t>注意：将你的书签页与其他能力分隔开来</t>
+    <t>注意：將你的書籤頁與其他能力分隔開來</t>
   </si>
   <si>
     <t>收支紀錄</t>
@@ -4420,7 +4420,7 @@
     <t>技能購買</t>
   </si>
   <si>
-    <t>检定</t>
+    <t>檢定</t>
   </si>
   <si>
     <t>氷之髮髻</t>
@@ -4486,13 +4486,13 @@
     <t>S級支線</t>
   </si>
   <si>
-    <t>储存分數</t>
+    <t>儲存分數</t>
   </si>
   <si>
     <t>XP</t>
   </si>
   <si>
-    <t>剩余分數</t>
+    <t>剩餘分數</t>
   </si>
   <si>
     <t>自學計算</t>
@@ -4510,28 +4510,28 @@
     <t>目前等級</t>
   </si>
   <si>
-    <t>装备位</t>
-  </si>
-  <si>
-    <t>随身物品</t>
-  </si>
-  <si>
-    <t>未携带物品</t>
+    <t>裝備位</t>
+  </si>
+  <si>
+    <t>隨身物品</t>
+  </si>
+  <si>
+    <t>未攜帶物品</t>
   </si>
   <si>
     <t>目標等級</t>
   </si>
   <si>
-    <t>头盔位</t>
+    <t>頭盔位</t>
   </si>
   <si>
     <t>所需XP</t>
   </si>
   <si>
-    <t>项链位</t>
-  </si>
-  <si>
-    <t>披风位</t>
+    <t>項鍊位</t>
+  </si>
+  <si>
+    <t>披風位</t>
   </si>
   <si>
     <t>專長種類</t>
@@ -4543,7 +4543,7 @@
     <t>本角卡由Sora製作、檢查。若有任何使用上的問題，歡迎電子郵件(a24631481@gmail.com)詢問。</t>
   </si>
   <si>
-    <t>护腕位</t>
+    <t>護腕位</t>
   </si>
   <si>
     <t>小計</t>
@@ -4552,10 +4552,10 @@
     <t>造物規則</t>
   </si>
   <si>
-    <t>腰带位</t>
-  </si>
-  <si>
-    <t>鞋袜位</t>
+    <t>腰帶位</t>
+  </si>
+  <si>
+    <t>鞋襪位</t>
   </si>
   <si>
     <t>學徒長袍</t>
@@ -4579,10 +4579,10 @@
     <t>物品點數</t>
   </si>
   <si>
-    <t>饰品（护符）位</t>
-  </si>
-  <si>
-    <t>概念武装</t>
+    <t>飾品（護符）位</t>
+  </si>
+  <si>
+    <t>概念武裝</t>
   </si>
   <si>
     <t>圖紙價格</t>
@@ -4618,7 +4618,7 @@
     <t>維修費用</t>
   </si>
   <si>
-    <t>计算器</t>
+    <t>計算器</t>
   </si>
   <si>
     <t>──模擬卡片──</t>
@@ -4818,7 +4818,7 @@
     <t>冷峻黑長髮、青藍瞳孔</t>
   </si>
   <si>
-    <t>冷面心善、厭惡虛偽</t>
+    <t>冷麵心善、厭惡虛偽</t>
   </si>
   <si>
     <t>外貌協會成員</t>
@@ -4877,7 +4877,7 @@
 接下來的事，完全不需要他在場，但沒注意到對方看著他的眼神，沒有感激，只有被目睹了狼狽求饒後的羞憤與陰冷
 律師、媒體、說詞、剪接過的比賽畫面，一切像早就準備好一樣，他的防衛被說成暴力傾向，過去的打擊被解釋為「致命技巧」，規則一條一條落下來，乾淨、合理，卻毫無溫度
 他第一次發現，自己的手什麼也抓不住
-道場被迫關閉，祖父在輿論與現實的雙重壓力下病倒，最後連一句交代都沒留下。葬禮那天，有人來道場門口叫囂、投擲雜物，他卻只是沈默地站著，將指甲深深掐進掌心。那些他多年來修習的「克制」與「清澈」，在這一刻成了最諷刺的笑話。連握拳都顯得多餘
+道場被迫關閉，祖父在輿論與現實的雙重壓力下病倒，最後連一句交代都沒留下。葬禮那天，有人來道場門口叫囂、投擲雜物，他卻只是沈默地站著，將指甲深深掐進掌心。那些他多年來修習的「剋制」與「清澈」，在這一刻成了最諷刺的笑話。連握拳都顯得多餘
 那一刻，他是真的感到噁心
 不是憤怒，而是徹底的幻滅
 原來力量在這個世界裡，根本派不上用場
@@ -5344,7 +5344,7 @@
     <t>免疫困難地形</t>
   </si>
   <si>
-    <t>空白面具</t>
+    <t>空白麵具</t>
   </si>
   <si>
     <t>你不認識我</t>
@@ -5469,7 +5469,7 @@
   <si>
     <t>林澤，男，二十一歲。外表只是城市裡最不起眼的年輕人——沉默、瘦削，眼神乾淨得像沒故事。但如果你真正認識他就會發現那份乾淨，這只是他最擅長的偽裝。他出生在一個平凡的家庭，父母離婚後，他像被踢皮球一樣在親戚間轉來轉去。沒人想真正照顧他，大人們總是挑刺，想盡各種辦法把他送走。他開始學會說謊——說自己吃飽了、說自己不冷、說自己沒事，只求在能獨立之前保證自己不被餓死。
 他第一次偷東西是在七歲那年。不是為了刺激，也不是叛逆，只是因為餓了。他偷了一個麵包，被老闆抓住。在老闆報警的恐懼下，他哭著跪下來，說自己好幾天沒吃飯，快餓死了才不得已偷東西，老闆這才心軟放過了他。那一天，他學會了把演戲當作武器，也明白想活下去，就得靠自己爭取。
-十五歲那年，林澤被街頭混混盯上。他不夠能打，也不夠狠，但他夠聰明。他懂得把恐懼藏起來，懂得用眼神裝得無所謂，甚至能笑著和人聊天，下一秒就把對方的錢包從口袋裡抽走。他在城市的縫隙裡活著：地下通道、夜市、網咖、廢棄大樓。他靠偷竊換飯吃，靠謊言換安全。他能偽裝成迷路的學生、倒霉的打工仔、剛失戀的可憐人，甚至扮成熱心志工，笑著幫你提行李，順手摸走你的手機。他能在幾分鐘內學會一個人的語氣、習慣與走路姿勢，說謊時眼睛乾淨得讓人相信他才是受害者。靠著這份天賦，他的“工作”開始“進階”——替人偷資料、偷車牌、調包物品，甚至把假文件塞進真正的檔案裡。他做得越來越熟練，把這一切融入生命裏，戴著面具遊走在各個角落。
+十五歲那年，林澤被街頭混混盯上。他不夠能打，也不夠狠，但他夠聰明。他懂得把恐懼藏起來，懂得用眼神裝得無所謂，甚至能笑著和人聊天，下一秒就把對方的錢包從口袋裡抽走。他在城市的縫隙裡活著：地下通道、夜市、網咖、廢棄大樓。他靠偷竊換飯吃，靠謊言換安全。他能偽裝成迷路的學生、倒黴的打工仔、剛失戀的可憐人，甚至扮成熱心志工，笑著幫你提行李，順手摸走你的手機。他能在幾分鐘內學會一個人的語氣、習慣與走路姿勢，說謊時眼睛乾淨得讓人相信他才是受害者。靠著這份天賦，他的“工作”開始“進階”——替人偷資料、偷車牌、調包物品，甚至把假文件塞進真正的檔案裡。他做得越來越熟練，把這一切融入生命裡，戴著面具遊走在各個角落。
 他住在一間狹小的出租屋裡，抽屜放著假證件與不同名字的銀行卡，唯一算重要的物品只有一雙手套，那個是一次進行任務時順回來的戰利品。當時富裕的時間只夠他再取走一樣東西，內心的直覺告訴他這個東西會對他有幫助，他便把它帶走了。不知道是不是他的錯覺戴上手套後進行工作的時候變得更加得心應手，從此以後便一直戴著不曾取下。一路走來他靠的不是勇敢，而是一張又一張的面具。他有很多名字，但沒有一個真正屬於他。他嘴上說「人活著不需要原則」，卻仍保留底線——從不傷害小孩。不是因為善良，而是因為他知道一旦跨過那條線，就再也回不了頭。直到某天，他的手機跳出一條訊息：「想明白生命的意義嗎？想真正地……活著嗎？」他的手指習慣性的停在No上很久，直到螢幕快熄滅的前一刻，還是選擇忠於內心按按下了Yes......</t>
   </si>
   <si>
@@ -7266,7 +7266,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="564">
+  <cellXfs count="565">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -8829,6 +8829,9 @@
     <xf borderId="9" fillId="22" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="42" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -21116,7 +21119,7 @@
         <v>604</v>
       </c>
       <c r="BO54" s="50"/>
-      <c r="BP54" s="272" t="b">
+      <c r="BP54" s="564" t="b">
         <v>0</v>
       </c>
       <c r="BQ54" s="50"/>
@@ -21136,7 +21139,7 @@
       <c r="BX54" s="49"/>
       <c r="BY54" s="50"/>
       <c r="BZ54" s="274" t="str">
-        <f>"+"&amp;if(BJ54="一阶",min(V21,V22),max(V21,V22))</f>
+        <f>"+"&amp;if(BJ54="一階",min(V21,V22),max(V21,V22))</f>
         <v>+2</v>
       </c>
       <c r="CA54" s="50"/>
@@ -53130,7 +53133,7 @@
     <dataValidation type="list" allowBlank="1" sqref="CS155">
       <formula1>'空白卡'!$CZ$165:$DA191</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="请点击并输入一个范围中的值" sqref="CQ5 CQ7 CQ9 CQ11 CQ13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="請點擊並輸入一個範圍中的值" sqref="CQ5 CQ7 CQ9 CQ11 CQ13">
       <formula1>'天賦 3xx'!$B:$B</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="CK179">
@@ -53164,7 +53167,7 @@
       <formula1>"-,男,女,不明,男女皆有"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BJ54">
-      <formula1>"一阶,二阶,三阶,四阶,五阶"</formula1>
+      <formula1>"一階,二階,三階,四階,五階"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="CI170">
       <formula1>"-,500,D500,D1000,DD500,DD1000,C1000,C2000,CC1000,CC2000,B2000,B4000,BB2000,BB4000,A4000,A8000,AA4000,AA8000,S8000,S16000,SS8000,SS16000"</formula1>
